--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1316,6 +1316,33 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>Value of the Source column in expansion_options.csv that counts as GSOO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ACIL Allen LNG price</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>netback_pricing_default</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Default state of the dashboard's LNG netback pricing switch. TRUE = ACIL Allen price formation is on unless turned off, which is the methodology behind the 2026 GSOO and the only mode in which an international price disciplines domestic prices. Overridden per run by the sidebar switch or --netback-pricing</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -866,25 +866,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capacity model</t>
+          <t>Data centre demand</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>discount_rate_default</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.07000000000000001</v>
+          <t>datacentre_series_path</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>file path</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NPV discount rate for the perfect-foresight capacity MIP</t>
+          <t>Optional: a spreadsheet holding a YEAR-BY-YEAR data centre demand series (Year column + NSW/VIC columns in PJ/yr), used instead of the flat cells for the states it covers. "none" (or blank) = the sidebar box starts empty and the lever behaves as it always has. This is a DEFAULT, not a lock: the box is editable and --dc-file overrides it. See src/data/datacentre_demand_example.csv</t>
         </is>
       </c>
     </row>
@@ -896,20 +898,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>peak_day_weight</t>
+          <t>discount_rate_default</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Days represented by the annual peak representative day (adequacy)</t>
+          <t>NPV discount rate for the perfect-foresight capacity MIP</t>
         </is>
       </c>
     </row>
@@ -921,20 +923,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>terminal_earliest</t>
+          <t>peak_day_weight</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2028</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>days</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Earliest build year for an LNG import terminal</t>
+          <t>Days represented by the annual peak representative day (adequacy)</t>
         </is>
       </c>
     </row>
@@ -946,11 +948,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>capacity_base_year</t>
+          <t>terminal_earliest</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -959,32 +961,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Discounting base year</t>
+          <t>Earliest build year for an LNG import terminal</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ACIL Allen LNG price</t>
+          <t>Capacity model</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>oil_link_fixed</t>
+          <t>capacity_base_year</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.4</v>
+        <v>2025</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>US$/mmbtu</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.9: FC in P_LNG=(FC+S*Pb)/(FX*C)</t>
+          <t>Discounting base year</t>
         </is>
       </c>
     </row>
@@ -996,20 +998,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>oil_link_slope</t>
+          <t>oil_link_fixed</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>US$/mmbtu</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.9: S, slope to Brent</t>
+          <t>ACIL Allen (14 Nov 2025) B.9: FC in P_LNG=(FC+S*Pb)/(FX*C)</t>
         </is>
       </c>
     </row>
@@ -1021,20 +1023,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>fx_usd_per_aud</t>
+          <t>oil_link_slope</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.66</v>
+        <v>0.12</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>US$/A$</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.9: FX</t>
+          <t>ACIL Allen (14 Nov 2025) B.9: S, slope to Brent</t>
         </is>
       </c>
     </row>
@@ -1046,20 +1048,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gj_per_mmbtu</t>
+          <t>fx_usd_per_aud</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.055</v>
+        <v>0.66</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GJ/mmbtu</t>
+          <t>US$/A$</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.9: C</t>
+          <t>ACIL Allen (14 Nov 2025) B.9: FX</t>
         </is>
       </c>
     </row>
@@ -1071,20 +1073,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>gj_per_mmbtu</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.8</v>
+        <v>1.055</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A$/GJ</t>
+          <t>GJ/mmbtu</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.11.1: US$0.56/mmbtu average shipping</t>
+          <t>ACIL Allen (14 Nov 2025) B.9: C</t>
         </is>
       </c>
     </row>
@@ -1096,11 +1098,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>regasification</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1109,7 +1111,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.11.2: allowance in all cases</t>
+          <t>ACIL Allen (14 Nov 2025) B.11.1: US$0.56/mmbtu average shipping</t>
         </is>
       </c>
     </row>
@@ -1121,11 +1123,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>export_netback_deduction</t>
+          <t>regasification</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.87</v>
+        <v>1.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1134,7 +1136,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NOT PUBLISHED by ACIL Allen or the ACCC. Avoidable liquefaction (plant SRMC + fuel gas) plus shipping, ACCC netback framework; midpoint of the public US$1.5-2.5/mmbtu range at FX 0.66, C 1.055. A CHOICE, NOT A SOURCE - the first number to test if a netback result matters.</t>
+          <t>ACIL Allen (14 Nov 2025) B.11.2: allowance in all cases</t>
         </is>
       </c>
     </row>
@@ -1146,11 +1148,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>code_price_cap</t>
+          <t>export_netback_deduction</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>2.87</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1159,32 +1161,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gas Market Code cap, ACIL Allen (14 Nov 2025) 2.3.1; applied as a ceiling on the LNG netback per ACIL Allen (14 Jul 2023) 4.1. Self-terminating: once the netback falls below it the ceiling stops binding.</t>
+          <t>NOT PUBLISHED by ACIL Allen or the ACCC. Avoidable liquefaction (plant SRMC + fuel gas) plus shipping, ACCC netback framework; midpoint of the public US$1.5-2.5/mmbtu range at FX 0.66, C 1.055. A CHOICE, NOT A SOURCE - the first number to test if a netback result matters.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LNG trains</t>
+          <t>ACIL Allen LNG price</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lng_nameplate_tj_day</t>
+          <t>code_price_cap</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3680</v>
+        <v>12</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TJ/day</t>
+          <t>A$/GJ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Total east coast liquefaction nameplate (100% utilisation). Mirrors lng_daily_target in lng_parameters.csv. This is the PHYSICAL ceiling on exports under netback pricing - a train cannot liquefy more than it can liquefy, however attractive the netback.</t>
+          <t>Gas Market Code cap, ACIL Allen (14 Nov 2025) 2.3.1; applied as a ceiling on the LNG netback per ACIL Allen (14 Jul 2023) 4.1. Self-terminating: once the netback falls below it the ceiling stops binding.</t>
         </is>
       </c>
     </row>
@@ -1196,22 +1198,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lng_train_shares</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>APLNG:0.357,GLNG:0.31,QCLNG:0.333</t>
-        </is>
+          <t>lng_nameplate_tj_day</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3680</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>node:share</t>
+          <t>TJ/day</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Each train's share of nameplate. Mirrors the *_factor rows in lng_parameters.csv.</t>
+          <t>Total east coast liquefaction nameplate (100% utilisation). Mirrors lng_daily_target in lng_parameters.csv. This is the PHYSICAL ceiling on exports under netback pricing - a train cannot liquefy more than it can liquefy, however attractive the netback.</t>
         </is>
       </c>
     </row>
@@ -1223,72 +1223,72 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>lng_foundation_share</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.93</v>
+          <t>lng_train_shares</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>APLNG:0.357,GLNG:0.31,QCLNG:0.333</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>node:share</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Share of planned export volume committed under long-term foundation SPAs: take-or-pay, therefore price-insensitive, served whatever the netback. The remainder is the uncontracted spot tail that bids at the netback and can be outbid by a domestic buyer or taken by a reservation. DERIVED FROM PUBLIC DATA: the ACCC publishes Queensland LNG producers' uncontracted gas each quarter and reported 22 PJ available for Q1 2026 (ACCC, east coast gas supply outlook, Q1 2026); against ~325-330 PJ of quarterly exports that is ~7% uncontracted, hence 0.93. Structure confirmed by ACIL Allen (14 Nov 2025) 2.3.2: 'the supply under foundation customers is untouched in our modelling, LNG exporters then supply the domestic market and export further gas via spot cargoes'. ONE QUARTER's figure, so treat as a KEY SENSITIVITY - it sets how much export volume is contestable at all.</t>
+          <t>Each train's share of nameplate. Mirrors the *_factor rows in lng_parameters.csv.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gas reservation</t>
+          <t>LNG trains</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>reservation_respects_contracts</t>
+          <t>lng_foundation_share</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1=yes, 0=no</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Default for whether a reservation may only take UNCONTRACTED export volume. 1: the reservation bites on the spot tail first and is capped at (1 - lng_foundation_share) of planned volume, so foundation SPAs are not broken - which is how the Heads of Agreement with the east coast LNG exporters actually works. 0: the reservation takes its share of ALL export volume, foundation contracts included. The dashboard toggle overrides this.</t>
+          <t>Share of planned export volume committed under long-term foundation SPAs: take-or-pay, therefore price-insensitive, served whatever the netback. The remainder is the uncontracted spot tail that bids at the netback and can be outbid by a domestic buyer or taken by a reservation. DERIVED FROM PUBLIC DATA: the ACCC publishes Queensland LNG producers' uncontracted gas each quarter and reported 22 PJ available for Q1 2026 (ACCC, east coast gas supply outlook, Q1 2026); against ~325-330 PJ of quarterly exports that is ~7% uncontracted, hence 0.93. Structure confirmed by ACIL Allen (14 Nov 2025) 2.3.2: 'the supply under foundation customers is untouched in our modelling, LNG exporters then supply the domestic market and export further gas via spot cargoes'. ONE QUARTER's figure, so treat as a KEY SENSITIVITY - it sets how much export volume is contestable at all.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Capacity model</t>
+          <t>Gas reservation</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gsoo_expansions_only</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+          <t>reservation_respects_contracts</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>1=yes, 0=no</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Default for the GSOO-only expansion filter. FALSE = the capacity layer may choose any candidate in expansion_options.csv; TRUE = only rows with Source=GSOO, i.e. the committed set in AEMO's 2026 GSOO/VGPR. Overridden per run by the dashboard toggle or --gsoo-expansions-only</t>
+          <t>Default for whether a reservation may only take UNCONTRACTED export volume. 1: the reservation bites on the spot tail first and is capped at (1 - lng_foundation_share) of planned volume, so foundation SPAs are not broken - which is how the Heads of Agreement with the east coast LNG exporters actually works. 0: the reservation takes its share of ALL export volume, foundation contracts included. The dashboard toggle overrides this.</t>
         </is>
       </c>
     </row>
@@ -1300,47 +1300,74 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>expansion_source_gsoo</t>
+          <t>gsoo_expansions_only</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GSOO</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Value of the Source column in expansion_options.csv that counts as GSOO</t>
+          <t>Default for the GSOO-only expansion filter. FALSE = the capacity layer may choose any candidate in expansion_options.csv; TRUE = only rows with Source=GSOO, i.e. the committed set in AEMO's 2026 GSOO/VGPR. Overridden per run by the dashboard toggle or --gsoo-expansions-only</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Capacity model</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>expansion_source_gsoo</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GSOO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Value of the Source column in expansion_options.csv that counts as GSOO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>ACIL Allen LNG price</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>netback_pricing_default</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Default state of the dashboard's LNG netback pricing switch. TRUE = ACIL Allen price formation is on unless turned off, which is the methodology behind the 2026 GSOO and the only mode in which an international price disciplines domestic prices. Overridden per run by the sidebar switch or --netback-pricing</t>
         </is>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>APLNG:0.357,GLNG:0.31,QCLNG:0.333</t>
+          <t>APLNG:0.3682,GLNG:0.3023,QCLNG:0.3295</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Each train's share of nameplate. Mirrors the *_factor rows in lng_parameters.csv.</t>
+          <t>2026 GSOO 'G26 Processing Transmission Storage Facilities', LNG Export sheet: APLNG 9.5, GLNG 7.8, QCLNG 8.5 Mtpa</t>
         </is>
       </c>
     </row>
@@ -1370,6 +1370,31 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>Default state of the dashboard's LNG netback pricing switch. TRUE = ACIL Allen price formation is on unless turned off, which is the methodology behind the 2026 GSOO and the only mode in which an international price disciplines domestic prices. Overridden per run by the sidebar switch or --netback-pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>storage_opening_fraction</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>fraction of capacity</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GARY's own. Inventory each year opens at this share of capacity and must close at or above it, so a year cannot create gas. Each year is solved independently, so this is an assumption either way.</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1395,6 +1395,522 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>GARY's own. Inventory each year opens at this share of capacity and must close at or above it, so a year cannot create gas. Each year is solved independently, so this is an assumption either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GSOO baselines</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>gsoo_baselines</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>StepChange,Accelerated,SlowerGrowth</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>slugs</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>The three 2026 GSOO demand scenarios GARY exposes as baselines. Was a SCENARIOS list repeated in four builder modules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>GSOO baselines</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>gsoo_index_base_year</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Year the GSOO sector indices are struck relative to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GSOO baselines</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>gsoo_index_last_year</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Last year the 2026 GSOO publishes. Indices clamp here and hold flat to horizon_end, so 2046-2050 is EXTRAPOLATION while ACIL Allen's price series keeps moving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Seasonality</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>summer_day_start</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>335</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>day of year</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Southern summer window used to strike the GPG winter:summer peak ratio (wraps the year end with summer_day_end).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Seasonality</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>summer_day_end</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>59</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>day of year</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>See summer_day_start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Demand history</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>gbb_recent_from</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>First year of GBB actuals averaged into the representative daily shape.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NT demand</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>nt_darwin_commercial_tjd</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TJ/day</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Darwin city-gate commercial / light-industrial load, held flat. AER AGP access arrangement review (AAR 2026-31) Table 2-1, 2024-25: Darwin distribution 0.3 + Townend Road 0.2 + Elliot 0.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NT demand</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>nt_gpg_base_tjd</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Darwin:33.4,Amadeus:11.0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>node:TJ/day</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>NT gas-fired generation by node in 2026, from AER AAR 2026-31 Table 2-1 delivery points, assigned by which side of Tennant Creek they sit on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NT demand</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>nt_gpg_decline</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>fraction/yr</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Gentle solar-driven decline on NT GPG. GARY's own; the NT is outside the NEM and the GSOO scenario framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Demand curves</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>reference_price_aud_gj</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>A$/GJ</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Demand-weighted mean nodal dual of the inelastic baseline. An elasticity measures response to a price DEVIATION, so it needs the model's own price, not a contract price. build_demand_curves.compute_reference_price() recomputes it from the cache and warns on drift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Demand curves</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>elasticity_short_run</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>own-price</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Short-run own-price elasticity of natural gas demand. Labandeira, Labeaga &amp; Lopez-Otero (2017), Energy Policy 102, 549-568, Table 6; significant at 1%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Demand curves</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>elasticity_asymmetry</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Raise-side elasticity = this x shed-side. Direction from Gately &amp; Huntington (2002), Energy Journal 23(1) 19-55: efficiency investment and plant closure from high prices do not reverse. THE RATIO IS A JUDGEMENT, NOT A MEASUREMENT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Demand curves</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>shed_multiples</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2,4,8</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>multiples of reference</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mass-market shed blocks are struck at these multiples of the reference price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Demand curves</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>raise_fractions</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.85,0.70,0.55</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>fractions of reference</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Industrial raise blocks are struck at these fractions of the reference price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Demand curves</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>winter_scale</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Damps the mass-market price response through the heating season. Default 1.0 = no adjustment. Kanellakis et al. (Energy Reports 8, 2022) find little daily gas price response through the heating season, so ~0.3-0.5 tests that evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Demand curves</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>massmarket_raises</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Whether mass-market demand RISES when gas is cheap. FALSE: Victoria banned gas connections in new homes from 1 Jan 2024 and the sector is in policy-driven structural decline, which a lower commodity price does not reverse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Demand curves</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>gpg_heat_rates</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>7.0,10.64,13.0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>GJ/MWh</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CCGT, NEM capacity-weighted average, OCGT. AEMO 2021 via Griffith University 2022-08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Demand curves</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>gpg_displaced_srmc</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>QLD:45,NSW:45,VIC:10,SA:10,NT:0</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>state:A$/MWh</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>What extra gas generation displaces at the margin, by jurisdiction. QLD/NSW black coal; VIC brown coal, mine-mouth (Hazelwood's private SRMC was put near $3/MWh, so gas essentially cannot displace it on running cost); SA imports over Heywood / Project EnergyConnect since Northern closed 9 May 2016; NT nothing - Darwin-Katherine is isolated and already &gt;80% gas, so zero is an honest 'cannot say'. THE SINGLE MOST INFLUENTIAL ASSUMPTION BEHIND THE GPG RESPONSE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Demand curves</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>gpg_expansion_cap</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>multiple of baseline</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>GPG may at most expand by this multiple of baseline demand. A modelling guardrail, not a finding: GARY models gas and not the NEM, and the fleet runs at ~9% of nameplate, so unbounded expansion would let an unmodelled electricity market set gas demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>GSOO baselines</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>gpg_nem_regions</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>NSW,SA,VIC,QLD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>regions</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>NEM regions whose GPG is re-based on the GSOO. The NT is outside the NEM and the GSOO scenario framework, so it is sized separately from the AER's AGP access arrangement; TAS has no modelled node.</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1911,6 +1911,83 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>NEM regions whose GPG is re-based on the GSOO. The NT is outside the NEM and the GSOO scenario framework, so it is sized separately from the AER's AGP access arrangement; TAS has no modelled node.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Demand shape</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>peak_shape_matching</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Reshape each city-gate node's daily profile year by year so its winter peak matches the 2026 GSOO's regional RC&amp;I daily maximum, holding annual energy fixed. Without it the 2026 daily shape is frozen for 26 years while the load behind it shifts from heating to industrial, so VIC's peak ran 22% over AEMO in 2026 and 43% over by 2045.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Demand shape</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>peak_shape_k_min</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Lower clip on the peakiness rescale. A region whose ANNUAL energy coverage is short cannot have its peak matched by reshaping alone (QLD: GARY carries no industrial outside Gladstone, TODO item 10), so the rescale is bounded and the residual is reported rather than forced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Demand shape</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>peak_shape_k_max</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Upper clip on the peakiness rescale. See peak_shape_k_min.</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -2061,7 +2061,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Multiplier on Melbourne/Adelaide/Sydney distribution demand over the winter window</t>
+          <t>THIS IS THE GSOO-CONSISTENT CASE: multiplier 1.0, so demand is exactly the calibrated GSOO series. Medium and High are STRESS cases layered on top of it, not alternative central forecasts.</t>
         </is>
       </c>
     </row>
@@ -2079,6 +2079,11 @@
       <c r="C3" t="n">
         <v>1.5</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Multiplier on Melbourne/Adelaide/Sydney distribution demand over winter_day_start..winter_day_end. STRESS CASE, and the dashboard default: it puts annual domestic energy 8-12% above the GSOO and Melbourne's peak day at ~1.8x AEMO's VIC RC&amp;I peak. Every headline GARY result is therefore a stressed run unless Winter is set to Low.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2093,6 +2098,11 @@
       </c>
       <c r="C4" t="n">
         <v>2.2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Severe stress case. Melbourne's peak day reaches ~2.6x AEMO's VIC RC&amp;I peak.</t>
+        </is>
       </c>
     </row>
     <row r="5">

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5.49</v>
+        <v>13.75</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Demand-weighted mean nodal dual of the inelastic baseline. An elasticity measures response to a price DEVIATION, so it needs the model's own price, not a contract price. build_demand_curves.compute_reference_price() recomputes it from the cache and warns on drift.</t>
+          <t>Demand-weighted mean nodal dual of the inelastic baseline (StepChange / Winter Medium / LNG Medium / netback), recomputed 29 Aug 2026 from the rebuilt cache. An elasticity measures response to a price DEVIATION, so it needs the model's own price, not a contract price. Was 5.49, struck before the supply-side depletion and demand-shape work roughly doubled the price level. build_demand_curves.compute_reference_price() recomputes it and main() warns if it has drifted more than $0.25.</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1630,66 +1630,70 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Demand curves</t>
+          <t>GSOO baselines</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>reference_price_aud_gj</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>13.75</v>
+          <t>gpg_nem_regions</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NSW,SA,VIC,QLD</t>
+        </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>A$/GJ</t>
+          <t>regions</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Demand-weighted mean nodal dual of the inelastic baseline (StepChange / Winter Medium / LNG Medium / netback), recomputed 29 Aug 2026 from the rebuilt cache. An elasticity measures response to a price DEVIATION, so it needs the model's own price, not a contract price. Was 5.49, struck before the supply-side depletion and demand-shape work roughly doubled the price level. build_demand_curves.compute_reference_price() recomputes it and main() warns if it has drifted more than $0.25.</t>
+          <t>NEM regions whose GPG is re-based on the GSOO. The NT is outside the NEM and the GSOO scenario framework, so it is sized separately from the AER's AGP access arrangement; TAS has no modelled node.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Demand curves</t>
+          <t>Demand shape</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>elasticity_short_run</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.18</v>
+          <t>peak_shape_matching</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>own-price</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Short-run own-price elasticity of natural gas demand. Labandeira, Labeaga &amp; Lopez-Otero (2017), Energy Policy 102, 549-568, Table 6; significant at 1%.</t>
+          <t>Reshape each city-gate node's daily profile year by year so its winter peak matches the 2026 GSOO's regional RC&amp;I daily maximum, holding annual energy fixed. Without it the 2026 daily shape is frozen for 26 years while the load behind it shifts from heating to industrial, so VIC's peak ran 22% over AEMO in 2026 and 43% over by 2045.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Demand curves</t>
+          <t>Demand shape</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>elasticity_asymmetry</t>
+          <t>peak_shape_k_min</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1698,294 +1702,30 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Raise-side elasticity = this x shed-side. Direction from Gately &amp; Huntington (2002), Energy Journal 23(1) 19-55: efficiency investment and plant closure from high prices do not reverse. THE RATIO IS A JUDGEMENT, NOT A MEASUREMENT.</t>
+          <t>Lower clip on the peakiness rescale. A region whose ANNUAL energy coverage is short cannot have its peak matched by reshaping alone (QLD: GARY carries no industrial outside Gladstone, TODO item 10), so the rescale is bounded and the residual is reported rather than forced.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Demand curves</t>
+          <t>Demand shape</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>shed_multiples</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2,4,8</t>
-        </is>
+          <t>peak_shape_k_max</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2.5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>multiples of reference</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
-        <is>
-          <t>Mass-market shed blocks are struck at these multiples of the reference price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Demand curves</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>raise_fractions</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>0.85,0.70,0.55</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>fractions of reference</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Industrial raise blocks are struck at these fractions of the reference price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Demand curves</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>winter_scale</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>multiple</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Damps the mass-market price response through the heating season. Default 1.0 = no adjustment. Kanellakis et al. (Energy Reports 8, 2022) find little daily gas price response through the heating season, so ~0.3-0.5 tests that evidence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Demand curves</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>massmarket_raises</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Whether mass-market demand RISES when gas is cheap. FALSE: Victoria banned gas connections in new homes from 1 Jan 2024 and the sector is in policy-driven structural decline, which a lower commodity price does not reverse.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Demand curves</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>gpg_heat_rates</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>7.0,10.64,13.0</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>GJ/MWh</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>CCGT, NEM capacity-weighted average, OCGT. AEMO 2021 via Griffith University 2022-08.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Demand curves</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>gpg_displaced_srmc</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>QLD:45,NSW:45,VIC:10,SA:10,NT:0</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>state:A$/MWh</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>What extra gas generation displaces at the margin, by jurisdiction. QLD/NSW black coal; VIC brown coal, mine-mouth (Hazelwood's private SRMC was put near $3/MWh, so gas essentially cannot displace it on running cost); SA imports over Heywood / Project EnergyConnect since Northern closed 9 May 2016; NT nothing - Darwin-Katherine is isolated and already &gt;80% gas, so zero is an honest 'cannot say'. THE SINGLE MOST INFLUENTIAL ASSUMPTION BEHIND THE GPG RESPONSE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Demand curves</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>gpg_expansion_cap</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>multiple of baseline</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>GPG may at most expand by this multiple of baseline demand. A modelling guardrail, not a finding: GARY models gas and not the NEM, and the fleet runs at ~9% of nameplate, so unbounded expansion would let an unmodelled electricity market set gas demand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>GSOO baselines</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>gpg_nem_regions</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>NSW,SA,VIC,QLD</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>regions</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>NEM regions whose GPG is re-based on the GSOO. The NT is outside the NEM and the GSOO scenario framework, so it is sized separately from the AER's AGP access arrangement; TAS has no modelled node.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Demand shape</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>peak_shape_matching</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Reshape each city-gate node's daily profile year by year so its winter peak matches the 2026 GSOO's regional RC&amp;I daily maximum, holding annual energy fixed. Without it the 2026 daily shape is frozen for 26 years while the load behind it shifts from heating to industrial, so VIC's peak ran 22% over AEMO in 2026 and 43% over by 2045.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Demand shape</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>peak_shape_k_min</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>multiple</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Lower clip on the peakiness rescale. A region whose ANNUAL energy coverage is short cannot have its peak matched by reshaping alone (QLD: GARY carries no industrial outside Gladstone, TODO item 10), so the rescale is bounded and the residual is reported rather than forced.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Demand shape</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>peak_shape_k_max</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>multiple</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
         <is>
           <t>Upper clip on the peakiness rescale. See peak_shape_k_min.</t>
         </is>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1728,6 +1728,33 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>Upper clip on the peakiness rescale. See peak_shape_k_min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Capacity model</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>allow_import_terminals</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Whether the capacity layer may build LNG IMPORT terminals -- a Type=Terminal candidate whose Target is one of import_nodes (Port Kembla, Geelong, Adelaide). FALSE removes them from the candidate set, so the east coast must meet demand from domestic supply and pipe. Field developments (Golden Beach, Beetaloo) are also Type=Terminal but target basin nodes, so they are NOT affected.</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1755,6 +1755,56 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>Whether the capacity layer may build LNG IMPORT terminals -- a Type=Terminal candidate whose Target is one of import_nodes (Port Kembla, Geelong, Adelaide). FALSE removes them from the candidate set, so the east coast must meet demand from domestic supply and pipe. Field developments (Golden Beach, Beetaloo) are also Type=Terminal but target basin nodes, so they are NOT affected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Cost coefficients</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>capex_annualisation_rate</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Share of a built project's CapEx charged to each single-year dispatch solve. The dispatch model covers one year and has no NPV to charge a lump sum against, so a build has to show up as an annual carrying cost or it would look free. GARY's own number, not a source: it sits above discount_rate_default because it stands in for return OF capital as well as return ON it. The capacity MIP does NOT use it -- that layer charges full CapEx once, discounted to the build year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Cost coefficients</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>storage_cycle_cost</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>A$/GJ</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Round-trip charge on storage, applied to injection AND withdrawal, so inventory cycles only when the seasonal price spread justifies it. GARY's own number, not a source. Read by both the dispatch model and the capacity MIP so the two layers value a store identically.</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -1315,7 +1315,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Default for the GSOO-only expansion filter. FALSE = the capacity layer may choose any candidate in expansion_options.csv; TRUE = only rows with Source=GSOO, i.e. the committed set in AEMO's 2026 GSOO/VGPR. Overridden per run by the dashboard toggle or --gsoo-expansions-only</t>
+          <t>Default for the GSOO-only expansion filter. FALSE = the capacity layer may choose any candidate in expansion_options.csv; TRUE = only rows with Source=GSOO, i.e. those AEMO NAMES in its 2026 GSOO material (the G26 Field Developments sheet for supply, the GSOO/VGPR project set for pipelines) -- whatever status AEMO gives them, Committed or Undeveloped alike. Source records where a candidate came from, NOT whether it is committed. Market rows are ones GARY researched from public announcements or built itself. Overridden per run by the dashboard toggle or --gsoo-expansions-only</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Value of the Source column in expansion_options.csv that counts as GSOO</t>
+          <t>Value of the Source column in expansion_options.csv that counts as AEMO-sourced</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -499,7 +499,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Last modelled year</t>
+          <t>Last SOLVED year. One year beyond horizon_report_end on purpose: a finite-horizon model exhausts its reserve tranches exactly at the last year it can see, so that year absorbs every accounting discrepancy and shows shortage. Solving one year past the reporting horizon pushes that artefact into a year nobody reads.</t>
         </is>
       </c>
     </row>
@@ -1805,6 +1805,31 @@
       <c r="E54" t="inlineStr">
         <is>
           <t>Round-trip charge on storage, applied to injection AND withdrawal, so inventory cycles only when the seasonal price spread justifies it. GARY's own number, not a source. Read by both the dispatch model and the capacity MIP so the two layers value a store identically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Horizon</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>horizon_report_end</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Last year PRESENTED. Results beyond this are solved but trimmed off before they reach the dashboard or a caller -- see solve.solve_scenario. Keep it strictly below horizon_end.</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario_Levers" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LNG_Anchors" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segment_Weights" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LNG_Contracts" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +53,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2562,4 +2567,611 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Queensland LNG foundation contract profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Source: ACCC Gas Inquiry 2017-2030, June 2025 interim update on the east coast gas market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Chart 1 -- remaining contracted exports to 2036 against reserves, resources and domestic purchases (PJ),</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ACCC analysis of data obtained from gas producers, as at January 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Narrative anchors, quoted:</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "The LNG producers' foundation contracts will expire from 2031."</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "a sharp drop off in exports and domestic contracted gas after 2035, which reflects the expiration of</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   LNG producer foundation contracts"</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "Some contracts have options to extend the supply period based on mutual agreement ... making exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   end dates uncertain. Therefore, significant export volumes may extend beyond 2036."</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>REMAINING CONTRACTED EXPORTS, PJ (ACCC Chart 1) -- these three are AEMO/ACCC figures, not GARY's</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Producer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Contracted_exports_PJ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2P_reserves_PJ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2C_resources_PJ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Net_domestic_purchases_PJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>APLNG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>6497</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10339</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3757</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GLNG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4515</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4882</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1233</v>
+      </c>
+      <c r="E15" t="n">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>QCLNG</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5289</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5728</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2770</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16301</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20949</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7760</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ANNUAL PROFILE. The PJ total is ACCC's; the YEAR-BY-YEAR SHAPE is GARY's, fitted to it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>flat while contracts run, half weight in 2036, zero from 2037, scaled so the series sums to 16,301 PJ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ACCC publishes the total and the timing in words, not a per-year series, so the shape is an</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>interpretation of 'expire from 2031 / sharp drop after 2035'. It is the first thing to test if a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>result turns on export volumes after 2030.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Contracted_PJ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>foundation contracts running</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>foundation contracts running</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>foundation contracts running</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>foundation contracts running</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>foundation contracts running</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>foundation contracts running</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>foundation contracts running</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>foundation contracts running</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>foundation contracts running</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>foundation contracts running</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>foundation contracts running</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B37" t="n">
+        <v>708.7</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sharp drop off after 2035 (ACCC); partial year of coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2046</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2047</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2049</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2050</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2051</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>foundation contracts expired -- export volume fully contestable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1835,6 +1835,85 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>Last year PRESENTED. Results beyond this are solved but trimmed off before they reach the dashboard or a caller -- see solve.solve_scenario. Keep it strictly below horizon_end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dashboard defaults</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>winter_default</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Winter stress level the dashboard opens on. LOW is the GSOO-consistent case (multiplier 1.0). It used to open on Medium, which is a 1.5x STRESS case -- 8-12% above GSOO annual energy with Melbourne's peak day at ~1.8x AEMO's VIC RC&amp;I peak -- so every headline figure was a stressed run unless someone moved the slider. Medium and High remain available; they are stress cases layered on the baseline, not alternative forecasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Dashboard defaults</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>lng_default</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Global LNG price level the dashboard opens on. Under netback pricing this lever selects a PRICE path, not an export volume: Medium is the run's own GSOO scenario path, so it is the internally consistent choice. Low is ACIL Allen's Accelerated Transition path and High its Slower Growth path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Dashboard defaults</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>mip_gap_default</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Relative MIP gap for the capacity layer. Matches solve_scenario's own default; the dashboard slider used to open at 0.01, which is a wider tolerance than any headless run used. That matters more since field developments carry derived CapEx in the tens of billions -- 1% of the objective is enough to hide a build decision.</t>
         </is>
       </c>
     </row>
@@ -2653,9 +2732,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
@@ -2766,7 +2843,6 @@
         <v>2512</v>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
@@ -2802,7 +2878,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Winter stress level the dashboard opens on. LOW is the GSOO-consistent case (multiplier 1.0). It used to open on Medium, which is a 1.5x STRESS case -- 8-12% above GSOO annual energy with Melbourne's peak day at ~1.8x AEMO's VIC RC&amp;I peak -- so every headline figure was a stressed run unless someone moved the slider. Medium and High remain available; they are stress cases layered on the baseline, not alternative forecasts.</t>
+          <t>Winter level the dashboard opens on. MEDIUM is the central GSOO case (multiplier 1.0, AEMO's weather-averaged series). Low is an unseasonably warm winter (0.91x) and High a deliberate stress (1.5x) beyond any observed winter.</t>
         </is>
       </c>
     </row>
@@ -1983,11 +1983,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>THIS IS THE GSOO-CONSISTENT CASE: multiplier 1.0, so demand is exactly the calibrated GSOO series. Medium and High are STRESS cases layered on top of it, not alternative central forecasts.</t>
+          <t>UNSEASONABLY WARM WINTER. 0.91x, the warmest of the seven full winters in the Bulletin Board record (2019-2025), measured on southern PIPE demand over the winter window and DETRENDED first: the raw series falls 2.6%/yr on structural decline, which is not weather. Residuals run 0.911 (2023) to 1.076 (2022), sd 0.046. This is the low-demand weather case, not a forecast.</t>
         </is>
       </c>
     </row>
@@ -2003,11 +2003,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Multiplier on Melbourne/Adelaide/Sydney distribution demand over winter_day_start..winter_day_end. STRESS CASE, and the dashboard default: it puts annual domestic energy 8-12% above the GSOO and Melbourne's peak day at ~1.8x AEMO's VIC RC&amp;I peak. Every headline GARY result is therefore a stressed run unless Winter is set to Low.</t>
+          <t>THE CENTRAL GSOO CASE: multiplier 1.0, so demand is exactly the calibrated GSOO series, which AEMO publishes weather-averaged. This is the default and the level to use for anything read as an outlook.</t>
         </is>
       </c>
     </row>
@@ -2023,11 +2023,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Severe stress case. Melbourne's peak day reaches ~2.6x AEMO's VIC RC&amp;I peak.</t>
+          <t>STRESS CASE, deliberately beyond observed weather. 1.5x puts annual domestic energy 8-12% above the GSOO and Melbourne's peak day at ~1.8x AEMO's VIC RC&amp;I peak. For reference the COLDEST winter in the Bulletin Board record is only 1.08x detrended, so this is an adequacy test rather than a cold-winter scenario. Set it to 1.08 if you want a weather-realistic cold case.</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1914,6 +1914,31 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>Relative MIP gap for the capacity layer. Matches solve_scenario's own default; the dashboard slider used to open at 0.01, which is a wider tolerance than any headless run used. That matters more since field developments carry derived CapEx in the tens of billions -- 1% of the objective is enough to hide a build decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Capacity model</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>rep_bins_per_month</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Load bins per month in the capacity layer's representative days. 1 reproduces the old single monthly MEAN day, which flattens the load-duration curve inside the month: a mild day and a cold snap in the same July became one average July day, and the marginal supply differs between them. Measured 30 Aug 2026 at 1 bin, the MIP planned ~44 PJ/yr LESS southern production than the 365-day dispatch layer drew, three years running, exhausting the southern tranches a year early and putting 16,008 TJ of shortage into 2032 the MIP never saw. Cost is roughly linear in the bin count: 3 bins is 37 representative days a year against 13.</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1939,6 +1939,33 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>Load bins per month in the capacity layer's representative days. 1 reproduces the old single monthly MEAN day, which flattens the load-duration curve inside the month: a mild day and a cold snap in the same July became one average July day, and the marginal supply differs between them. Measured 30 Aug 2026 at 1 bin, the MIP planned ~44 PJ/yr LESS southern production than the 365-day dispatch layer drew, three years running, exhausting the southern tranches a year early and putting 16,008 TJ of shortage into 2032 the MIP never saw. Cost is roughly linear in the bin count: 3 bins is 37 representative days a year against 13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Capacity model</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>rep_day_mode</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>medoid</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>mean|medoid</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>How each load bin becomes a representative day. MEDOID picks a REAL day -- the one whose total demand sits closest to the bin's mean. MEAN averages the bin. Averaging destroys COINCIDENCE, not just level: a real cold day is cold in Melbourne and Adelaide and Sydney at once, which is exactly when the corridors bind, while a mean spreads the same energy over node-day combinations that never co-occurred. The network then never looks tight and the investment layer sees no congestion to build around. Adding bins does not help because each bin is still an average -- 13, 37 and 61 representative days gave byte-identical build lists. Annual energy fidelity is unaffected (measured +2.09% medoid against +2.26% mean, both dominated by the peak day's extra weight).</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2051</v>
+        <v>2065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Last SOLVED year. One year beyond horizon_report_end on purpose: a finite-horizon model exhausts its reserve tranches exactly at the last year it can see, so that year absorbs every accounting discrepancy and shows shortage. Solving one year past the reporting horizon pushes that artefact into a year nobody reads.</t>
+          <t>Last SOLVED year. Well beyond horizon_report_end on purpose. The terminal salvage credit is de-discounted in get_scarcity_rents, so the Hotelling rent it implies grows at the discount rate and reaches the full salvage rate exactly at this year -- which means the last decade before it is contaminated by the horizon whatever the salvage price is. Solving to 2065 and reporting to 2050 puts that contaminated tail outside the window anyone reads. Series that end earlier (demand 2051, LNG prices 2051, GPG/industrial profiles 2045) hold their last published year across the padding; that is padding, not a forecast.</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2065</v>
+        <v>2051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Last SOLVED year. Well beyond horizon_report_end on purpose. The terminal salvage credit is de-discounted in get_scarcity_rents, so the Hotelling rent it implies grows at the discount rate and reaches the full salvage rate exactly at this year -- which means the last decade before it is contaminated by the horizon whatever the salvage price is. Solving to 2065 and reporting to 2050 puts that contaminated tail outside the window anyone reads. Series that end earlier (demand 2051, LNG prices 2051, GPG/industrial profiles 2045) hold their last published year across the padding; that is padding, not a forecast.</t>
+          <t>Last SOLVED year, one beyond horizon_report_end. Held at 2051 because that is where the published data ends (demand and ACIL Allen prices 2051, GPG/industrial profiles 2045). Padding further does NOT buy a cleaner answer: measured 2 Sep 2026, a 2065 pad put 14 extra years of held-flat demand against the same finite reserves and drove the Surat reserve dual from /bin/bash.00 to 4.42/GJ, manufacturing scarcity rather than removing an artefact. Fix the terminal value instead -- see TODO item 15.</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1966,6 +1966,56 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>How each load bin becomes a representative day. MEDOID picks a REAL day -- the one whose total demand sits closest to the bin's mean. MEAN averages the bin. Averaging destroys COINCIDENCE, not just level: a real cold day is cold in Melbourne and Adelaide and Sydney at once, which is exactly when the corridors bind, while a mean spreads the same energy over node-day combinations that never co-occurred. The network then never looks tight and the investment layer sees no congestion to build around. Adding bins does not help because each bin is still an average -- 13, 37 and 61 representative days gave byte-identical build lists. Annual energy fidelity is unaffected (measured +2.09% medoid against +2.26% mean, both dominated by the peak day's extra weight).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Capacity model</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>salvage_max_passes</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>passes</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>OFF by default, as a MEASURED negative result, not an oversight. The iteration works -- it converges geometrically in 4 passes (tau moves 1.48, 0.74, 0.37, 0.19) and it is better specified, measuring tau on the stock actually left at the horizon rather than on nameplate reserves. It changes almost nothing: exports 23,101 -&gt; 23,070 PJ and every rent identical to 2dp, for 40% more solve time. The reason is that the salvage credit and the reserve dual are PERFECTLY SUBSTITUTABLE -- both are linear in cumulative production -- so lowering the credit just raises the dual one-for-one (8.64/0.00, 2.57/1.77, 0.00/4.17, all totalling 8.07 or 4.17). Turn it back on only if reserve_limit is ever replaced by a per-year stock. See TODO item 16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Capacity model</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>salvage_tau_tol</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Stop iterating once no row moves its reserves-to-production ratio by more than this.</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -953,20 +953,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>terminal_earliest</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2028</v>
+          <t>asset_salvage</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Earliest build year for an LNG import terminal</t>
+          <t>TRUE/FALSE</t>
         </is>
       </c>
     </row>
@@ -978,11 +975,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>capacity_base_year</t>
+          <t>terminal_earliest</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -991,32 +988,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Discounting base year</t>
+          <t>Earliest build year for an LNG import terminal</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ACIL Allen LNG price</t>
+          <t>Capacity model</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>oil_link_fixed</t>
+          <t>capacity_base_year</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.4</v>
+        <v>2025</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>US$/mmbtu</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.9: FC in P_LNG=(FC+S*Pb)/(FX*C)</t>
+          <t>Discounting base year</t>
         </is>
       </c>
     </row>
@@ -1028,20 +1025,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>oil_link_slope</t>
+          <t>oil_link_fixed</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>US$/mmbtu</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.9: S, slope to Brent</t>
+          <t>ACIL Allen (14 Nov 2025) B.9: FC in P_LNG=(FC+S*Pb)/(FX*C)</t>
         </is>
       </c>
     </row>
@@ -1053,20 +1050,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fx_usd_per_aud</t>
+          <t>oil_link_slope</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.66</v>
+        <v>0.12</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>US$/A$</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.9: FX</t>
+          <t>ACIL Allen (14 Nov 2025) B.9: S, slope to Brent</t>
         </is>
       </c>
     </row>
@@ -1078,20 +1075,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>gj_per_mmbtu</t>
+          <t>fx_usd_per_aud</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.055</v>
+        <v>0.66</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GJ/mmbtu</t>
+          <t>US$/A$</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.9: C</t>
+          <t>ACIL Allen (14 Nov 2025) B.9: FX</t>
         </is>
       </c>
     </row>
@@ -1103,20 +1100,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>gj_per_mmbtu</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.8</v>
+        <v>1.055</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A$/GJ</t>
+          <t>GJ/mmbtu</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.11.1: US$0.56/mmbtu average shipping</t>
+          <t>ACIL Allen (14 Nov 2025) B.9: C</t>
         </is>
       </c>
     </row>
@@ -1128,11 +1125,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>regasification</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1141,7 +1138,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.11.2: allowance in all cases</t>
+          <t>ACIL Allen (14 Nov 2025) B.11.1: US$0.56/mmbtu average shipping</t>
         </is>
       </c>
     </row>
@@ -1153,11 +1150,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>export_netback_deduction</t>
+          <t>regasification</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.87</v>
+        <v>1.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1166,7 +1163,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NOT PUBLISHED by ACIL Allen or the ACCC. Avoidable liquefaction (plant SRMC + fuel gas) plus shipping, ACCC netback framework; midpoint of the public US$1.5-2.5/mmbtu range at FX 0.66, C 1.055. A CHOICE, NOT A SOURCE - the first number to test if a netback result matters.</t>
+          <t>ACIL Allen (14 Nov 2025) B.11.2: allowance in all cases</t>
         </is>
       </c>
     </row>
@@ -1178,11 +1175,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>code_price_cap</t>
+          <t>export_netback_deduction</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>2.87</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1191,32 +1188,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gas Market Code cap, ACIL Allen (14 Nov 2025) 2.3.1; applied as a ceiling on the LNG netback per ACIL Allen (14 Jul 2023) 4.1. Self-terminating: once the netback falls below it the ceiling stops binding.</t>
+          <t>NOT PUBLISHED by ACIL Allen or the ACCC. Avoidable liquefaction (plant SRMC + fuel gas) plus shipping, ACCC netback framework; midpoint of the public US$1.5-2.5/mmbtu range at FX 0.66, C 1.055. A CHOICE, NOT A SOURCE - the first number to test if a netback result matters.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LNG trains</t>
+          <t>ACIL Allen LNG price</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lng_nameplate_tj_day</t>
+          <t>code_price_cap</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3680</v>
+        <v>12</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TJ/day</t>
+          <t>A$/GJ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Total east coast liquefaction nameplate (100% utilisation). Mirrors lng_daily_target in lng_parameters.csv. This is the PHYSICAL ceiling on exports under netback pricing - a train cannot liquefy more than it can liquefy, however attractive the netback.</t>
+          <t>Gas Market Code cap, ACIL Allen (14 Nov 2025) 2.3.1; applied as a ceiling on the LNG netback per ACIL Allen (14 Jul 2023) 4.1. Self-terminating: once the netback falls below it the ceiling stops binding.</t>
         </is>
       </c>
     </row>
@@ -1228,22 +1225,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>lng_train_shares</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>APLNG:0.3682,GLNG:0.3023,QCLNG:0.3295</t>
-        </is>
+          <t>lng_nameplate_tj_day</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3680</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>node:share</t>
+          <t>TJ/day</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026 GSOO 'G26 Processing Transmission Storage Facilities', LNG Export sheet: APLNG 9.5, GLNG 7.8, QCLNG 8.5 Mtpa</t>
+          <t>Total east coast liquefaction nameplate (100% utilisation). Mirrors lng_daily_target in lng_parameters.csv. This is the PHYSICAL ceiling on exports under netback pricing - a train cannot liquefy more than it can liquefy, however attractive the netback.</t>
         </is>
       </c>
     </row>
@@ -1255,72 +1250,72 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>lng_foundation_share</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.93</v>
+          <t>lng_train_shares</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>APLNG:0.3682,GLNG:0.3023,QCLNG:0.3295</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>node:share</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Share of planned export volume committed under long-term foundation SPAs: take-or-pay, therefore price-insensitive, served whatever the netback. The remainder is the uncontracted spot tail that bids at the netback and can be outbid by a domestic buyer or taken by a reservation. DERIVED FROM PUBLIC DATA: the ACCC publishes Queensland LNG producers' uncontracted gas each quarter and reported 22 PJ available for Q1 2026 (ACCC, east coast gas supply outlook, Q1 2026); against ~325-330 PJ of quarterly exports that is ~7% uncontracted, hence 0.93. Structure confirmed by ACIL Allen (14 Nov 2025) 2.3.2: 'the supply under foundation customers is untouched in our modelling, LNG exporters then supply the domestic market and export further gas via spot cargoes'. ONE QUARTER's figure, so treat as a KEY SENSITIVITY - it sets how much export volume is contestable at all.</t>
+          <t>2026 GSOO 'G26 Processing Transmission Storage Facilities', LNG Export sheet: APLNG 9.5, GLNG 7.8, QCLNG 8.5 Mtpa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gas reservation</t>
+          <t>LNG trains</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>reservation_respects_contracts</t>
+          <t>lng_foundation_share</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1=yes, 0=no</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Default for whether a reservation may only take UNCONTRACTED export volume. 1: the reservation bites on the spot tail first and is capped at (1 - lng_foundation_share) of planned volume, so foundation SPAs are not broken - which is how the Heads of Agreement with the east coast LNG exporters actually works. 0: the reservation takes its share of ALL export volume, foundation contracts included. The dashboard toggle overrides this.</t>
+          <t>Share of planned export volume committed under long-term foundation SPAs: take-or-pay, therefore price-insensitive, served whatever the netback. The remainder is the uncontracted spot tail that bids at the netback and can be outbid by a domestic buyer or taken by a reservation. DERIVED FROM PUBLIC DATA: the ACCC publishes Queensland LNG producers' uncontracted gas each quarter and reported 22 PJ available for Q1 2026 (ACCC, east coast gas supply outlook, Q1 2026); against ~325-330 PJ of quarterly exports that is ~7% uncontracted, hence 0.93. Structure confirmed by ACIL Allen (14 Nov 2025) 2.3.2: 'the supply under foundation customers is untouched in our modelling, LNG exporters then supply the domestic market and export further gas via spot cargoes'. ONE QUARTER's figure, so treat as a KEY SENSITIVITY - it sets how much export volume is contestable at all.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Capacity model</t>
+          <t>Gas reservation</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>gsoo_expansions_only</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+          <t>reservation_respects_contracts</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>1=yes, 0=no</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Default for the GSOO-only expansion filter. FALSE = the capacity layer may choose any candidate in expansion_options.csv; TRUE = only rows with Source=GSOO, i.e. those AEMO NAMES in its 2026 GSOO material (the G26 Field Developments sheet for supply, the GSOO/VGPR project set for pipelines) -- whatever status AEMO gives them, Committed or Undeveloped alike. Source records where a candidate came from, NOT whether it is committed. Market rows are ones GARY researched from public announcements or built itself. Overridden per run by the dashboard toggle or --gsoo-expansions-only</t>
+          <t>Default for whether a reservation may only take UNCONTRACTED export volume. 1: the reservation bites on the spot tail first and is capped at (1 - lng_foundation_share) of planned volume, so foundation SPAs are not broken - which is how the Heads of Agreement with the east coast LNG exporters actually works. 0: the reservation takes its share of ALL export volume, foundation contracts included. The dashboard toggle overrides this.</t>
         </is>
       </c>
     </row>
@@ -1332,101 +1327,101 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>expansion_source_gsoo</t>
+          <t>gsoo_expansions_only</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GSOO</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Value of the Source column in expansion_options.csv that counts as AEMO-sourced</t>
+          <t>Default for the GSOO-only expansion filter. FALSE = the capacity layer may choose any candidate in expansion_options.csv; TRUE = only rows with Source=GSOO, i.e. those AEMO NAMES in its 2026 GSOO material (the G26 Field Developments sheet for supply, the GSOO/VGPR project set for pipelines) -- whatever status AEMO gives them, Committed or Undeveloped alike. Source records where a candidate came from, NOT whether it is committed. Market rows are ones GARY researched from public announcements or built itself. Overridden per run by the dashboard toggle or --gsoo-expansions-only</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ACIL Allen LNG price</t>
+          <t>Capacity model</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>netback_pricing_default</t>
+          <t>expansion_source_gsoo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>GSOO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>label</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Default state of the dashboard's LNG netback pricing switch. TRUE = ACIL Allen price formation is on unless turned off, which is the methodology behind the 2026 GSOO and the only mode in which an international price disciplines domestic prices. Overridden per run by the sidebar switch or --netback-pricing</t>
+          <t>Value of the Source column in expansion_options.csv that counts as AEMO-sourced</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>ACIL Allen LNG price</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>storage_opening_fraction</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.5</v>
+          <t>netback_pricing_default</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>fraction of capacity</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GARY's own. Inventory each year opens at this share of capacity and must close at or above it, so a year cannot create gas. Each year is solved independently, so this is an assumption either way.</t>
+          <t>Default state of the dashboard's LNG netback pricing switch. TRUE = ACIL Allen price formation is on unless turned off, which is the methodology behind the 2026 GSOO and the only mode in which an international price disciplines domestic prices. Overridden per run by the sidebar switch or --netback-pricing</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GSOO baselines</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>gsoo_baselines</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>StepChange,Accelerated,SlowerGrowth</t>
-        </is>
+          <t>storage_opening_fraction</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>slugs</t>
+          <t>fraction of capacity</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>The three 2026 GSOO demand scenarios GARY exposes as baselines. Was a SCENARIOS list repeated in four builder modules.</t>
+          <t>GARY's own. Inventory each year opens at this share of capacity and must close at or above it, so a year cannot create gas. Each year is solved independently, so this is an assumption either way.</t>
         </is>
       </c>
     </row>
@@ -1438,20 +1433,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>gsoo_index_base_year</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>2026</v>
+          <t>gsoo_baselines</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>StepChange,Accelerated,SlowerGrowth</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>slugs</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Year the GSOO sector indices are struck relative to.</t>
+          <t>The three 2026 GSOO demand scenarios GARY exposes as baselines. Was a SCENARIOS list repeated in four builder modules.</t>
         </is>
       </c>
     </row>
@@ -1463,11 +1460,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>gsoo_index_last_year</t>
+          <t>gsoo_index_base_year</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2045</v>
+        <v>2026</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1476,32 +1473,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Last year the 2026 GSOO publishes. Indices clamp here and hold flat to horizon_end, so 2046-2050 is EXTRAPOLATION while ACIL Allen's price series keeps moving.</t>
+          <t>Year the GSOO sector indices are struck relative to.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Seasonality</t>
+          <t>GSOO baselines</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>summer_day_start</t>
+          <t>gsoo_index_last_year</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>335</v>
+        <v>2045</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>day of year</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southern summer window used to strike the GPG winter:summer peak ratio (wraps the year end with summer_day_end).</t>
+          <t>Last year the 2026 GSOO publishes. Indices clamp here and hold flat to horizon_end, so 2046-2050 is EXTRAPOLATION while ACIL Allen's price series keeps moving.</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1510,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>summer_day_end</t>
+          <t>summer_day_start</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>59</v>
+        <v>335</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1526,57 +1523,57 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>See summer_day_start.</t>
+          <t>Southern summer window used to strike the GPG winter:summer peak ratio (wraps the year end with summer_day_end).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Demand history</t>
+          <t>Seasonality</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>gbb_recent_from</t>
+          <t>summer_day_end</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2022</v>
+        <v>59</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>day of year</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>First year of GBB actuals averaged into the representative daily shape.</t>
+          <t>See summer_day_start.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NT demand</t>
+          <t>Demand history</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nt_darwin_commercial_tjd</t>
+          <t>gbb_recent_from</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.6</v>
+        <v>2022</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TJ/day</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Darwin city-gate commercial / light-industrial load, held flat. AER AGP access arrangement review (AAR 2026-31) Table 2-1, 2024-25: Darwin distribution 0.3 + Townend Road 0.2 + Elliot 0.1.</t>
+          <t>First year of GBB actuals averaged into the representative daily shape.</t>
         </is>
       </c>
     </row>
@@ -1588,22 +1585,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nt_gpg_base_tjd</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Darwin:33.4,Amadeus:11.0</t>
-        </is>
+          <t>nt_darwin_commercial_tjd</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>node:TJ/day</t>
+          <t>TJ/day</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NT gas-fired generation by node in 2026, from AER AAR 2026-31 Table 2-1 delivery points, assigned by which side of Tennant Creek they sit on.</t>
+          <t>Darwin city-gate commercial / light-industrial load, held flat. AER AGP access arrangement review (AAR 2026-31) Table 2-1, 2024-25: Darwin distribution 0.3 + Townend Road 0.2 + Elliot 0.1.</t>
         </is>
       </c>
     </row>
@@ -1615,74 +1610,74 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nt_gpg_decline</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.008</v>
+          <t>nt_gpg_base_tjd</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Darwin:33.4,Amadeus:11.0</t>
+        </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>fraction/yr</t>
+          <t>node:TJ/day</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gentle solar-driven decline on NT GPG. GARY's own; the NT is outside the NEM and the GSOO scenario framework.</t>
+          <t>NT gas-fired generation by node in 2026, from AER AAR 2026-31 Table 2-1 delivery points, assigned by which side of Tennant Creek they sit on.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GSOO baselines</t>
+          <t>NT demand</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>gpg_nem_regions</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>NSW,SA,VIC,QLD</t>
-        </is>
+          <t>nt_gpg_decline</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.008</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>regions</t>
+          <t>fraction/yr</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NEM regions whose GPG is re-based on the GSOO. The NT is outside the NEM and the GSOO scenario framework, so it is sized separately from the AER's AGP access arrangement; TAS has no modelled node.</t>
+          <t>Gentle solar-driven decline on NT GPG. GARY's own; the NT is outside the NEM and the GSOO scenario framework.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Demand shape</t>
+          <t>GSOO baselines</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>peak_shape_matching</t>
+          <t>gpg_nem_regions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>NSW,SA,VIC,QLD</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>regions</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Reshape each city-gate node's daily profile year by year so its winter peak matches the 2026 GSOO's regional RC&amp;I daily maximum, holding annual energy fixed. Without it the 2026 daily shape is frozen for 26 years while the load behind it shifts from heating to industrial, so VIC's peak ran 22% over AEMO in 2026 and 43% over by 2045.</t>
+          <t>NEM regions whose GPG is re-based on the GSOO. The NT is outside the NEM and the GSOO scenario framework, so it is sized separately from the AER's AGP access arrangement; TAS has no modelled node.</t>
         </is>
       </c>
     </row>
@@ -1694,20 +1689,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>peak_shape_k_min</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.25</v>
+          <t>peak_shape_matching</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>multiple</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lower clip on the peakiness rescale. A region whose ANNUAL energy coverage is short cannot have its peak matched by reshaping alone (QLD: GARY carries no industrial outside Gladstone, TODO item 10), so the rescale is bounded and the residual is reported rather than forced.</t>
+          <t>Reshape each city-gate node's daily profile year by year so its winter peak matches the 2026 GSOO's regional RC&amp;I daily maximum, holding annual energy fixed. Without it the 2026 daily shape is frozen for 26 years while the load behind it shifts from heating to industrial, so VIC's peak ran 22% over AEMO in 2026 and 43% over by 2045.</t>
         </is>
       </c>
     </row>
@@ -1719,11 +1716,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>peak_shape_k_max</t>
+          <t>peak_shape_k_min</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1732,59 +1729,59 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Upper clip on the peakiness rescale. See peak_shape_k_min.</t>
+          <t>Lower clip on the peakiness rescale. A region whose ANNUAL energy coverage is short cannot have its peak matched by reshaping alone (QLD: GARY carries no industrial outside Gladstone, TODO item 10), so the rescale is bounded and the residual is reported rather than forced.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Capacity model</t>
+          <t>Demand shape</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>allow_import_terminals</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+          <t>peak_shape_k_max</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2.5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Whether the capacity layer may build LNG IMPORT terminals -- a Type=Terminal candidate whose Target is one of import_nodes (Port Kembla, Geelong, Adelaide). FALSE removes them from the candidate set, so the east coast must meet demand from domestic supply and pipe. Field developments (Golden Beach, Beetaloo) are also Type=Terminal but target basin nodes, so they are NOT affected.</t>
+          <t>Upper clip on the peakiness rescale. See peak_shape_k_min.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cost coefficients</t>
+          <t>Capacity model</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>capex_annualisation_rate</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.08</v>
+          <t>allow_import_terminals</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Share of a built project's CapEx charged to each single-year dispatch solve. The dispatch model covers one year and has no NPV to charge a lump sum against, so a build has to show up as an annual carrying cost or it would look free. GARY's own number, not a source: it sits above discount_rate_default because it stands in for return OF capital as well as return ON it. The capacity MIP does NOT use it -- that layer charges full CapEx once, discounted to the build year.</t>
+          <t>Whether the capacity layer may build LNG IMPORT terminals -- a Type=Terminal candidate whose Target is one of import_nodes (Port Kembla, Geelong, Adelaide). FALSE removes them from the candidate set, so the east coast must meet demand from domestic supply and pipe. Field developments (Golden Beach, Beetaloo) are also Type=Terminal but target basin nodes, so they are NOT affected.</t>
         </is>
       </c>
     </row>
@@ -1796,72 +1793,70 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>storage_cycle_cost</t>
+          <t>capex_annualisation_rate</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>A$/GJ</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Round-trip charge on storage, applied to injection AND withdrawal, so inventory cycles only when the seasonal price spread justifies it. GARY's own number, not a source. Read by both the dispatch model and the capacity MIP so the two layers value a store identically.</t>
+          <t>Share of a built project's CapEx charged to each single-year dispatch solve. The dispatch model covers one year and has no NPV to charge a lump sum against, so a build has to show up as an annual carrying cost or it would look free. GARY's own number, not a source: it sits above discount_rate_default because it stands in for return OF capital as well as return ON it. The capacity MIP does NOT use it -- that layer charges full CapEx once, discounted to the build year.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Horizon</t>
+          <t>Cost coefficients</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>horizon_report_end</t>
+          <t>storage_cycle_cost</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2050</v>
+        <v>0.5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>A$/GJ</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Last year PRESENTED. Results beyond this are solved but trimmed off before they reach the dashboard or a caller -- see solve.solve_scenario. Keep it strictly below horizon_end.</t>
+          <t>Round-trip charge on storage, applied to injection AND withdrawal, so inventory cycles only when the seasonal price spread justifies it. GARY's own number, not a source. Read by both the dispatch model and the capacity MIP so the two layers value a store identically.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Dashboard defaults</t>
+          <t>Horizon</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>winter_default</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>horizon_report_end</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2050</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Winter level the dashboard opens on. MEDIUM is the central GSOO case (multiplier 1.0, AEMO's weather-averaged series). Low is an unseasonably warm winter (0.91x) and High a deliberate stress (1.5x) beyond any observed winter.</t>
+          <t>Last year PRESENTED. Results beyond this are solved but trimmed off before they reach the dashboard or a caller -- see solve.solve_scenario. Keep it strictly below horizon_end.</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1868,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>lng_default</t>
+          <t>winter_default</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1888,7 +1883,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Global LNG price level the dashboard opens on. Under netback pricing this lever selects a PRICE path, not an export volume: Medium is the run's own GSOO scenario path, so it is the internally consistent choice. Low is ACIL Allen's Accelerated Transition path and High its Slower Growth path.</t>
+          <t>Winter level the dashboard opens on. MEDIUM is the central GSOO case (multiplier 1.0, AEMO's weather-averaged series). Low is an unseasonably warm winter (0.91x) and High a deliberate stress (1.5x) beyond any observed winter.</t>
         </is>
       </c>
     </row>
@@ -1900,45 +1895,47 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>mip_gap_default</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>0.005</v>
+          <t>lng_default</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Relative MIP gap for the capacity layer. Matches solve_scenario's own default; the dashboard slider used to open at 0.01, which is a wider tolerance than any headless run used. That matters more since field developments carry derived CapEx in the tens of billions -- 1% of the objective is enough to hide a build decision.</t>
+          <t>Global LNG price level the dashboard opens on. Under netback pricing this lever selects a PRICE path, not an export volume: Medium is the run's own GSOO scenario path, so it is the internally consistent choice. Low is ACIL Allen's Accelerated Transition path and High its Slower Growth path.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Capacity model</t>
+          <t>Dashboard defaults</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>rep_bins_per_month</t>
+          <t>mip_gap_default</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>0.005</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Load bins per month in the capacity layer's representative days. 1 reproduces the old single monthly MEAN day, which flattens the load-duration curve inside the month: a mild day and a cold snap in the same July became one average July day, and the marginal supply differs between them. Measured 30 Aug 2026 at 1 bin, the MIP planned ~44 PJ/yr LESS southern production than the 365-day dispatch layer drew, three years running, exhausting the southern tranches a year early and putting 16,008 TJ of shortage into 2032 the MIP never saw. Cost is roughly linear in the bin count: 3 bins is 37 representative days a year against 13.</t>
+          <t>Relative MIP gap for the capacity layer. Matches solve_scenario's own default; the dashboard slider used to open at 0.01, which is a wider tolerance than any headless run used. That matters more since field developments carry derived CapEx in the tens of billions -- 1% of the objective is enough to hide a build decision.</t>
         </is>
       </c>
     </row>
@@ -1950,22 +1947,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>rep_day_mode</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>medoid</t>
-        </is>
+          <t>rep_bins_per_month</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>mean|medoid</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>How each load bin becomes a representative day. MEDOID picks a REAL day -- the one whose total demand sits closest to the bin's mean. MEAN averages the bin. Averaging destroys COINCIDENCE, not just level: a real cold day is cold in Melbourne and Adelaide and Sydney at once, which is exactly when the corridors bind, while a mean spreads the same energy over node-day combinations that never co-occurred. The network then never looks tight and the investment layer sees no congestion to build around. Adding bins does not help because each bin is still an average -- 13, 37 and 61 representative days gave byte-identical build lists. Annual energy fidelity is unaffected (measured +2.09% medoid against +2.26% mean, both dominated by the peak day's extra weight).</t>
+          <t>Load bins per month in the capacity layer's representative days. 1 reproduces the old single monthly MEAN day, which flattens the load-duration curve inside the month: a mild day and a cold snap in the same July became one average July day, and the marginal supply differs between them. Measured 30 Aug 2026 at 1 bin, the MIP planned ~44 PJ/yr LESS southern production than the 365-day dispatch layer drew, three years running, exhausting the southern tranches a year early and putting 16,008 TJ of shortage into 2032 the MIP never saw. Cost is roughly linear in the bin count: 3 bins is 37 representative days a year against 13.</t>
         </is>
       </c>
     </row>
@@ -1977,20 +1972,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>salvage_max_passes</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>0</v>
+          <t>rep_day_mode</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>medoid</t>
+        </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>passes</t>
+          <t>mean|medoid</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OFF by default, as a MEASURED negative result, not an oversight. The iteration works -- it converges geometrically in 4 passes (tau moves 1.48, 0.74, 0.37, 0.19) and it is better specified, measuring tau on the stock actually left at the horizon rather than on nameplate reserves. It changes almost nothing: exports 23,101 -&gt; 23,070 PJ and every rent identical to 2dp, for 40% more solve time. The reason is that the salvage credit and the reserve dual are PERFECTLY SUBSTITUTABLE -- both are linear in cumulative production -- so lowering the credit just raises the dual one-for-one (8.64/0.00, 2.57/1.77, 0.00/4.17, all totalling 8.07 or 4.17). Turn it back on only if reserve_limit is ever replaced by a per-year stock. See TODO item 16.</t>
+          <t>How each load bin becomes a representative day. MEDOID picks a REAL day -- the one whose total demand sits closest to the bin's mean. MEAN averages the bin. Averaging destroys COINCIDENCE, not just level: a real cold day is cold in Melbourne and Adelaide and Sydney at once, which is exactly when the corridors bind, while a mean spreads the same energy over node-day combinations that never co-occurred. The network then never looks tight and the investment layer sees no congestion to build around. Adding bins does not help because each bin is still an average -- 13, 37 and 61 representative days gave byte-identical build lists. Annual energy fidelity is unaffected (measured +2.09% medoid against +2.26% mean, both dominated by the peak day's extra weight).</t>
         </is>
       </c>
     </row>
@@ -2002,18 +1999,43 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>salvage_max_passes</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>passes</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>OFF by default, as a MEASURED negative result, not an oversight. The iteration works -- it converges geometrically in 4 passes (tau moves 1.48, 0.74, 0.37, 0.19) and it is better specified, measuring tau on the stock actually left at the horizon rather than on nameplate reserves. It changes almost nothing: exports 23,101 -&gt; 23,070 PJ and every rent identical to 2dp, for 40% more solve time. The reason is that the salvage credit and the reserve dual are PERFECTLY SUBSTITUTABLE -- both are linear in cumulative production -- so lowering the credit just raises the dual one-for-one (8.64/0.00, 2.57/1.77, 0.00/4.17, all totalling 8.07 or 4.17). Turn it back on only if reserve_limit is ever replaced by a per-year stock. See TODO item 16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Capacity model</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>salvage_tau_tol</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="C63" t="n">
         <v>0.25</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Stop iterating once no row moves its reserves-to-production ratio by more than this.</t>
         </is>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -975,20 +975,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>terminal_earliest</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2028</v>
+          <t>salvage_route_capacity</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>TRUE/FALSE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Earliest build year for an LNG import terminal</t>
+          <t>Strike the terminal salvage credit on the disposal routes a basin's gas can ACTUALLY take, weighted by each route's bottleneck capacity, instead of on the single dearest destination less the tariff to reach it. Only the basins feeding the LNG trains are affected -- a basin sitting inside the market it supplies has one disposal price and keeps the old rule. Surat has two prices that differ by the liquefaction-shipping-regasification wedge ($9.79/GJ landed-import parity against $6.37/GJ export netback in 2051) and only 349 TJ/day of corridor to the dearer one against 6,300 TJ/day of deliverability, so the old rule paid the whole basin a price 6% of its gas could reach. ON. Set FALSE to reproduce runs from before the change; it moves every Queensland scarcity rent, so every result moves.</t>
         </is>
       </c>
     </row>
@@ -1000,11 +1002,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capacity_base_year</t>
+          <t>terminal_earliest</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1013,32 +1015,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Discounting base year</t>
+          <t>Earliest build year for an LNG import terminal</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ACIL Allen LNG price</t>
+          <t>Capacity model</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>oil_link_fixed</t>
+          <t>capacity_base_year</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.4</v>
+        <v>2025</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>US$/mmbtu</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.9: FC in P_LNG=(FC+S*Pb)/(FX*C)</t>
+          <t>Discounting base year</t>
         </is>
       </c>
     </row>
@@ -1050,20 +1052,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>oil_link_slope</t>
+          <t>oil_link_fixed</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>US$/mmbtu</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.9: S, slope to Brent</t>
+          <t>ACIL Allen (14 Nov 2025) B.9: FC in P_LNG=(FC+S*Pb)/(FX*C)</t>
         </is>
       </c>
     </row>
@@ -1075,20 +1077,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>fx_usd_per_aud</t>
+          <t>oil_link_slope</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.66</v>
+        <v>0.12</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>US$/A$</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.9: FX</t>
+          <t>ACIL Allen (14 Nov 2025) B.9: S, slope to Brent</t>
         </is>
       </c>
     </row>
@@ -1100,20 +1102,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gj_per_mmbtu</t>
+          <t>fx_usd_per_aud</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.055</v>
+        <v>0.66</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GJ/mmbtu</t>
+          <t>US$/A$</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.9: C</t>
+          <t>ACIL Allen (14 Nov 2025) B.9: FX</t>
         </is>
       </c>
     </row>
@@ -1125,20 +1127,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>gj_per_mmbtu</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.8</v>
+        <v>1.055</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A$/GJ</t>
+          <t>GJ/mmbtu</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.11.1: US$0.56/mmbtu average shipping</t>
+          <t>ACIL Allen (14 Nov 2025) B.9: C</t>
         </is>
       </c>
     </row>
@@ -1150,11 +1152,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>regasification</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1163,7 +1165,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ACIL Allen (14 Nov 2025) B.11.2: allowance in all cases</t>
+          <t>ACIL Allen (14 Nov 2025) B.11.1: US$0.56/mmbtu average shipping</t>
         </is>
       </c>
     </row>
@@ -1175,11 +1177,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>export_netback_deduction</t>
+          <t>regasification</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.87</v>
+        <v>1.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1188,7 +1190,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NOT PUBLISHED by ACIL Allen or the ACCC. Avoidable liquefaction (plant SRMC + fuel gas) plus shipping, ACCC netback framework; midpoint of the public US$1.5-2.5/mmbtu range at FX 0.66, C 1.055. A CHOICE, NOT A SOURCE - the first number to test if a netback result matters.</t>
+          <t>ACIL Allen (14 Nov 2025) B.11.2: allowance in all cases</t>
         </is>
       </c>
     </row>
@@ -1200,11 +1202,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>code_price_cap</t>
+          <t>export_netback_deduction</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>2.87</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1213,32 +1215,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gas Market Code cap, ACIL Allen (14 Nov 2025) 2.3.1; applied as a ceiling on the LNG netback per ACIL Allen (14 Jul 2023) 4.1. Self-terminating: once the netback falls below it the ceiling stops binding.</t>
+          <t>NOT PUBLISHED by ACIL Allen or the ACCC. Avoidable liquefaction (plant SRMC + fuel gas) plus shipping, ACCC netback framework; midpoint of the public US$1.5-2.5/mmbtu range at FX 0.66, C 1.055. A CHOICE, NOT A SOURCE - the first number to test if a netback result matters.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LNG trains</t>
+          <t>ACIL Allen LNG price</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>lng_nameplate_tj_day</t>
+          <t>code_price_cap</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3680</v>
+        <v>12</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TJ/day</t>
+          <t>A$/GJ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Total east coast liquefaction nameplate (100% utilisation). Mirrors lng_daily_target in lng_parameters.csv. This is the PHYSICAL ceiling on exports under netback pricing - a train cannot liquefy more than it can liquefy, however attractive the netback.</t>
+          <t>Gas Market Code cap, ACIL Allen (14 Nov 2025) 2.3.1; applied as a ceiling on the LNG netback per ACIL Allen (14 Jul 2023) 4.1. Self-terminating: once the netback falls below it the ceiling stops binding.</t>
         </is>
       </c>
     </row>
@@ -1250,22 +1252,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>lng_train_shares</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>APLNG:0.3682,GLNG:0.3023,QCLNG:0.3295</t>
-        </is>
+          <t>lng_nameplate_tj_day</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3680</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>node:share</t>
+          <t>TJ/day</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026 GSOO 'G26 Processing Transmission Storage Facilities', LNG Export sheet: APLNG 9.5, GLNG 7.8, QCLNG 8.5 Mtpa</t>
+          <t>Total east coast liquefaction nameplate (100% utilisation). Mirrors lng_daily_target in lng_parameters.csv. This is the PHYSICAL ceiling on exports under netback pricing - a train cannot liquefy more than it can liquefy, however attractive the netback.</t>
         </is>
       </c>
     </row>
@@ -1277,72 +1277,72 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>lng_foundation_share</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.93</v>
+          <t>lng_train_shares</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>APLNG:0.3682,GLNG:0.3023,QCLNG:0.3295</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>node:share</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Share of planned export volume committed under long-term foundation SPAs: take-or-pay, therefore price-insensitive, served whatever the netback. The remainder is the uncontracted spot tail that bids at the netback and can be outbid by a domestic buyer or taken by a reservation. DERIVED FROM PUBLIC DATA: the ACCC publishes Queensland LNG producers' uncontracted gas each quarter and reported 22 PJ available for Q1 2026 (ACCC, east coast gas supply outlook, Q1 2026); against ~325-330 PJ of quarterly exports that is ~7% uncontracted, hence 0.93. Structure confirmed by ACIL Allen (14 Nov 2025) 2.3.2: 'the supply under foundation customers is untouched in our modelling, LNG exporters then supply the domestic market and export further gas via spot cargoes'. ONE QUARTER's figure, so treat as a KEY SENSITIVITY - it sets how much export volume is contestable at all.</t>
+          <t>2026 GSOO 'G26 Processing Transmission Storage Facilities', LNG Export sheet: APLNG 9.5, GLNG 7.8, QCLNG 8.5 Mtpa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Gas reservation</t>
+          <t>LNG trains</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>reservation_respects_contracts</t>
+          <t>lng_foundation_share</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1=yes, 0=no</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Default for whether a reservation may only take UNCONTRACTED export volume. 1: the reservation bites on the spot tail first and is capped at (1 - lng_foundation_share) of planned volume, so foundation SPAs are not broken - which is how the Heads of Agreement with the east coast LNG exporters actually works. 0: the reservation takes its share of ALL export volume, foundation contracts included. The dashboard toggle overrides this.</t>
+          <t>Share of planned export volume committed under long-term foundation SPAs: take-or-pay, therefore price-insensitive, served whatever the netback. The remainder is the uncontracted spot tail that bids at the netback and can be outbid by a domestic buyer or taken by a reservation. DERIVED FROM PUBLIC DATA: the ACCC publishes Queensland LNG producers' uncontracted gas each quarter and reported 22 PJ available for Q1 2026 (ACCC, east coast gas supply outlook, Q1 2026); against ~325-330 PJ of quarterly exports that is ~7% uncontracted, hence 0.93. Structure confirmed by ACIL Allen (14 Nov 2025) 2.3.2: 'the supply under foundation customers is untouched in our modelling, LNG exporters then supply the domestic market and export further gas via spot cargoes'. ONE QUARTER's figure, so treat as a KEY SENSITIVITY - it sets how much export volume is contestable at all.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Capacity model</t>
+          <t>Gas reservation</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>gsoo_expansions_only</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+          <t>reservation_respects_contracts</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>1=yes, 0=no</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Default for the GSOO-only expansion filter. FALSE = the capacity layer may choose any candidate in expansion_options.csv; TRUE = only rows with Source=GSOO, i.e. those AEMO NAMES in its 2026 GSOO material (the G26 Field Developments sheet for supply, the GSOO/VGPR project set for pipelines) -- whatever status AEMO gives them, Committed or Undeveloped alike. Source records where a candidate came from, NOT whether it is committed. Market rows are ones GARY researched from public announcements or built itself. Overridden per run by the dashboard toggle or --gsoo-expansions-only</t>
+          <t>Default for whether a reservation may only take UNCONTRACTED export volume. 1: the reservation bites on the spot tail first and is capped at (1 - lng_foundation_share) of planned volume, so foundation SPAs are not broken - which is how the Heads of Agreement with the east coast LNG exporters actually works. 0: the reservation takes its share of ALL export volume, foundation contracts included. The dashboard toggle overrides this.</t>
         </is>
       </c>
     </row>
@@ -1354,101 +1354,101 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>expansion_source_gsoo</t>
+          <t>gsoo_expansions_only</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GSOO</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Value of the Source column in expansion_options.csv that counts as AEMO-sourced</t>
+          <t>Default for the GSOO-only expansion filter. FALSE = the capacity layer may choose any candidate in expansion_options.csv; TRUE = only rows with Source=GSOO, i.e. those AEMO NAMES in its 2026 GSOO material (the G26 Field Developments sheet for supply, the GSOO/VGPR project set for pipelines) -- whatever status AEMO gives them, Committed or Undeveloped alike. Source records where a candidate came from, NOT whether it is committed. Market rows are ones GARY researched from public announcements or built itself. Overridden per run by the dashboard toggle or --gsoo-expansions-only</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ACIL Allen LNG price</t>
+          <t>Capacity model</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>netback_pricing_default</t>
+          <t>expansion_source_gsoo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>GSOO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>label</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Default state of the dashboard's LNG netback pricing switch. TRUE = ACIL Allen price formation is on unless turned off, which is the methodology behind the 2026 GSOO and the only mode in which an international price disciplines domestic prices. Overridden per run by the sidebar switch or --netback-pricing</t>
+          <t>Value of the Source column in expansion_options.csv that counts as AEMO-sourced</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>ACIL Allen LNG price</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>storage_opening_fraction</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.5</v>
+          <t>netback_pricing_default</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>fraction of capacity</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GARY's own. Inventory each year opens at this share of capacity and must close at or above it, so a year cannot create gas. Each year is solved independently, so this is an assumption either way.</t>
+          <t>Default state of the dashboard's LNG netback pricing switch. TRUE = ACIL Allen price formation is on unless turned off, which is the methodology behind the 2026 GSOO and the only mode in which an international price disciplines domestic prices. Overridden per run by the sidebar switch or --netback-pricing</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GSOO baselines</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>gsoo_baselines</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>StepChange,Accelerated,SlowerGrowth</t>
-        </is>
+          <t>storage_opening_fraction</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>slugs</t>
+          <t>fraction of capacity</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>The three 2026 GSOO demand scenarios GARY exposes as baselines. Was a SCENARIOS list repeated in four builder modules.</t>
+          <t>GARY's own. Inventory each year opens at this share of capacity and must close at or above it, so a year cannot create gas. Each year is solved independently, so this is an assumption either way.</t>
         </is>
       </c>
     </row>
@@ -1460,20 +1460,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>gsoo_index_base_year</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>2026</v>
+          <t>gsoo_baselines</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>StepChange,Accelerated,SlowerGrowth</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>slugs</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Year the GSOO sector indices are struck relative to.</t>
+          <t>The three 2026 GSOO demand scenarios GARY exposes as baselines. Was a SCENARIOS list repeated in four builder modules.</t>
         </is>
       </c>
     </row>
@@ -1485,11 +1487,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>gsoo_index_last_year</t>
+          <t>gsoo_index_base_year</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2045</v>
+        <v>2026</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1498,32 +1500,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Last year the 2026 GSOO publishes. Indices clamp here and hold flat to horizon_end, so 2046-2050 is EXTRAPOLATION while ACIL Allen's price series keeps moving.</t>
+          <t>Year the GSOO sector indices are struck relative to.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Seasonality</t>
+          <t>GSOO baselines</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>summer_day_start</t>
+          <t>gsoo_index_last_year</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>335</v>
+        <v>2045</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>day of year</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Southern summer window used to strike the GPG winter:summer peak ratio (wraps the year end with summer_day_end).</t>
+          <t>Last year the 2026 GSOO publishes. Indices clamp here and hold flat to horizon_end, so 2046-2050 is EXTRAPOLATION while ACIL Allen's price series keeps moving.</t>
         </is>
       </c>
     </row>
@@ -1535,11 +1537,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>summer_day_end</t>
+          <t>summer_day_start</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>59</v>
+        <v>335</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1548,57 +1550,57 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>See summer_day_start.</t>
+          <t>Southern summer window used to strike the GPG winter:summer peak ratio (wraps the year end with summer_day_end).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Demand history</t>
+          <t>Seasonality</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>gbb_recent_from</t>
+          <t>summer_day_end</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2022</v>
+        <v>59</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>day of year</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>First year of GBB actuals averaged into the representative daily shape.</t>
+          <t>See summer_day_start.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NT demand</t>
+          <t>Demand history</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nt_darwin_commercial_tjd</t>
+          <t>gbb_recent_from</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.6</v>
+        <v>2022</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TJ/day</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Darwin city-gate commercial / light-industrial load, held flat. AER AGP access arrangement review (AAR 2026-31) Table 2-1, 2024-25: Darwin distribution 0.3 + Townend Road 0.2 + Elliot 0.1.</t>
+          <t>First year of GBB actuals averaged into the representative daily shape.</t>
         </is>
       </c>
     </row>
@@ -1610,22 +1612,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nt_gpg_base_tjd</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Darwin:33.4,Amadeus:11.0</t>
-        </is>
+          <t>nt_darwin_commercial_tjd</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.6</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>node:TJ/day</t>
+          <t>TJ/day</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NT gas-fired generation by node in 2026, from AER AAR 2026-31 Table 2-1 delivery points, assigned by which side of Tennant Creek they sit on.</t>
+          <t>Darwin city-gate commercial / light-industrial load, held flat. AER AGP access arrangement review (AAR 2026-31) Table 2-1, 2024-25: Darwin distribution 0.3 + Townend Road 0.2 + Elliot 0.1.</t>
         </is>
       </c>
     </row>
@@ -1637,74 +1637,74 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nt_gpg_decline</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.008</v>
+          <t>nt_gpg_base_tjd</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Darwin:33.4,Amadeus:11.0</t>
+        </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>fraction/yr</t>
+          <t>node:TJ/day</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gentle solar-driven decline on NT GPG. GARY's own; the NT is outside the NEM and the GSOO scenario framework.</t>
+          <t>NT gas-fired generation by node in 2026, from AER AAR 2026-31 Table 2-1 delivery points, assigned by which side of Tennant Creek they sit on.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GSOO baselines</t>
+          <t>NT demand</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>gpg_nem_regions</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>NSW,SA,VIC,QLD</t>
-        </is>
+          <t>nt_gpg_decline</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.008</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>regions</t>
+          <t>fraction/yr</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>NEM regions whose GPG is re-based on the GSOO. The NT is outside the NEM and the GSOO scenario framework, so it is sized separately from the AER's AGP access arrangement; TAS has no modelled node.</t>
+          <t>Gentle solar-driven decline on NT GPG. GARY's own; the NT is outside the NEM and the GSOO scenario framework.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Demand shape</t>
+          <t>GSOO baselines</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>peak_shape_matching</t>
+          <t>gpg_nem_regions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>NSW,SA,VIC,QLD</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>regions</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Reshape each city-gate node's daily profile year by year so its winter peak matches the 2026 GSOO's regional RC&amp;I daily maximum, holding annual energy fixed. Without it the 2026 daily shape is frozen for 26 years while the load behind it shifts from heating to industrial, so VIC's peak ran 22% over AEMO in 2026 and 43% over by 2045.</t>
+          <t>NEM regions whose GPG is re-based on the GSOO. The NT is outside the NEM and the GSOO scenario framework, so it is sized separately from the AER's AGP access arrangement; TAS has no modelled node.</t>
         </is>
       </c>
     </row>
@@ -1716,20 +1716,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>peak_shape_k_min</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.25</v>
+          <t>peak_shape_matching</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>multiple</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lower clip on the peakiness rescale. A region whose ANNUAL energy coverage is short cannot have its peak matched by reshaping alone (QLD: GARY carries no industrial outside Gladstone, TODO item 10), so the rescale is bounded and the residual is reported rather than forced.</t>
+          <t>Reshape each city-gate node's daily profile year by year so its winter peak matches the 2026 GSOO's regional RC&amp;I daily maximum, holding annual energy fixed. Without it the 2026 daily shape is frozen for 26 years while the load behind it shifts from heating to industrial, so VIC's peak ran 22% over AEMO in 2026 and 43% over by 2045.</t>
         </is>
       </c>
     </row>
@@ -1741,11 +1743,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>peak_shape_k_max</t>
+          <t>peak_shape_k_min</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1754,59 +1756,59 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Upper clip on the peakiness rescale. See peak_shape_k_min.</t>
+          <t>Lower clip on the peakiness rescale. A region whose ANNUAL energy coverage is short cannot have its peak matched by reshaping alone (QLD: GARY carries no industrial outside Gladstone, TODO item 10), so the rescale is bounded and the residual is reported rather than forced.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Capacity model</t>
+          <t>Demand shape</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>allow_import_terminals</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+          <t>peak_shape_k_max</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2.5</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Whether the capacity layer may build LNG IMPORT terminals -- a Type=Terminal candidate whose Target is one of import_nodes (Port Kembla, Geelong, Adelaide). FALSE removes them from the candidate set, so the east coast must meet demand from domestic supply and pipe. Field developments (Golden Beach, Beetaloo) are also Type=Terminal but target basin nodes, so they are NOT affected.</t>
+          <t>Upper clip on the peakiness rescale. See peak_shape_k_min.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cost coefficients</t>
+          <t>Capacity model</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>capex_annualisation_rate</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.08</v>
+          <t>allow_import_terminals</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Share of a built project's CapEx charged to each single-year dispatch solve. The dispatch model covers one year and has no NPV to charge a lump sum against, so a build has to show up as an annual carrying cost or it would look free. GARY's own number, not a source: it sits above discount_rate_default because it stands in for return OF capital as well as return ON it. The capacity MIP does NOT use it -- that layer charges full CapEx once, discounted to the build year.</t>
+          <t>Whether the capacity layer may build LNG IMPORT terminals -- a Type=Terminal candidate whose Target is one of import_nodes (Port Kembla, Geelong, Adelaide). FALSE removes them from the candidate set, so the east coast must meet demand from domestic supply and pipe. Field developments (Golden Beach, Beetaloo) are also Type=Terminal but target basin nodes, so they are NOT affected.</t>
         </is>
       </c>
     </row>
@@ -1818,72 +1820,70 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>storage_cycle_cost</t>
+          <t>capex_annualisation_rate</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A$/GJ</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Round-trip charge on storage, applied to injection AND withdrawal, so inventory cycles only when the seasonal price spread justifies it. GARY's own number, not a source. Read by both the dispatch model and the capacity MIP so the two layers value a store identically.</t>
+          <t>Share of a built project's CapEx charged to each single-year dispatch solve. The dispatch model covers one year and has no NPV to charge a lump sum against, so a build has to show up as an annual carrying cost or it would look free. GARY's own number, not a source: it sits above discount_rate_default because it stands in for return OF capital as well as return ON it. The capacity MIP does NOT use it -- that layer charges full CapEx once, discounted to the build year.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Horizon</t>
+          <t>Cost coefficients</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>horizon_report_end</t>
+          <t>storage_cycle_cost</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2050</v>
+        <v>0.5</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>A$/GJ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Last year PRESENTED. Results beyond this are solved but trimmed off before they reach the dashboard or a caller -- see solve.solve_scenario. Keep it strictly below horizon_end.</t>
+          <t>Round-trip charge on storage, applied to injection AND withdrawal, so inventory cycles only when the seasonal price spread justifies it. GARY's own number, not a source. Read by both the dispatch model and the capacity MIP so the two layers value a store identically.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Dashboard defaults</t>
+          <t>Horizon</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>winter_default</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>horizon_report_end</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Winter level the dashboard opens on. MEDIUM is the central GSOO case (multiplier 1.0, AEMO's weather-averaged series). Low is an unseasonably warm winter (0.91x) and High a deliberate stress (1.5x) beyond any observed winter.</t>
+          <t>Last year PRESENTED. Results beyond this are solved but trimmed off before they reach the dashboard or a caller -- see solve.solve_scenario. Keep it strictly below horizon_end.</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>lng_default</t>
+          <t>winter_default</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Global LNG price level the dashboard opens on. Under netback pricing this lever selects a PRICE path, not an export volume: Medium is the run's own GSOO scenario path, so it is the internally consistent choice. Low is ACIL Allen's Accelerated Transition path and High its Slower Growth path.</t>
+          <t>Winter level the dashboard opens on. MEDIUM is the central GSOO case (multiplier 1.0, AEMO's weather-averaged series). Low is an unseasonably warm winter (0.91x) and High a deliberate stress (1.5x) beyond any observed winter.</t>
         </is>
       </c>
     </row>
@@ -1922,45 +1922,47 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>mip_gap_default</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>0.005</v>
+          <t>lng_default</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Relative MIP gap for the capacity layer. Matches solve_scenario's own default; the dashboard slider used to open at 0.01, which is a wider tolerance than any headless run used. That matters more since field developments carry derived CapEx in the tens of billions -- 1% of the objective is enough to hide a build decision.</t>
+          <t>Global LNG price level the dashboard opens on. Under netback pricing this lever selects a PRICE path, not an export volume: Medium is the run's own GSOO scenario path, so it is the internally consistent choice. Low is ACIL Allen's Accelerated Transition path and High its Slower Growth path.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Capacity model</t>
+          <t>Dashboard defaults</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>rep_bins_per_month</t>
+          <t>mip_gap_default</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>0.005</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Load bins per month in the capacity layer's representative days. 1 reproduces the old single monthly MEAN day, which flattens the load-duration curve inside the month: a mild day and a cold snap in the same July became one average July day, and the marginal supply differs between them. Measured 30 Aug 2026 at 1 bin, the MIP planned ~44 PJ/yr LESS southern production than the 365-day dispatch layer drew, three years running, exhausting the southern tranches a year early and putting 16,008 TJ of shortage into 2032 the MIP never saw. Cost is roughly linear in the bin count: 3 bins is 37 representative days a year against 13.</t>
+          <t>Relative MIP gap for the capacity layer. Matches solve_scenario's own default; the dashboard slider used to open at 0.01, which is a wider tolerance than any headless run used. That matters more since field developments carry derived CapEx in the tens of billions -- 1% of the objective is enough to hide a build decision.</t>
         </is>
       </c>
     </row>
@@ -1972,22 +1974,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>rep_day_mode</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>medoid</t>
-        </is>
+          <t>rep_bins_per_month</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>mean|medoid</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>How each load bin becomes a representative day. MEDOID picks a REAL day -- the one whose total demand sits closest to the bin's mean. MEAN averages the bin. Averaging destroys COINCIDENCE, not just level: a real cold day is cold in Melbourne and Adelaide and Sydney at once, which is exactly when the corridors bind, while a mean spreads the same energy over node-day combinations that never co-occurred. The network then never looks tight and the investment layer sees no congestion to build around. Adding bins does not help because each bin is still an average -- 13, 37 and 61 representative days gave byte-identical build lists. Annual energy fidelity is unaffected (measured +2.09% medoid against +2.26% mean, both dominated by the peak day's extra weight).</t>
+          <t>Load bins per month in the capacity layer's representative days. 1 reproduces the old single monthly MEAN day, which flattens the load-duration curve inside the month: a mild day and a cold snap in the same July became one average July day, and the marginal supply differs between them. Measured 30 Aug 2026 at 1 bin, the MIP planned ~44 PJ/yr LESS southern production than the 365-day dispatch layer drew, three years running, exhausting the southern tranches a year early and putting 16,008 TJ of shortage into 2032 the MIP never saw. Cost is roughly linear in the bin count: 3 bins is 37 representative days a year against 13.</t>
         </is>
       </c>
     </row>
@@ -1999,20 +1999,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>salvage_max_passes</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
+          <t>rep_day_mode</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>medoid</t>
+        </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>passes</t>
+          <t>mean|medoid</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OFF by default, as a MEASURED negative result, not an oversight. The iteration works -- it converges geometrically in 4 passes (tau moves 1.48, 0.74, 0.37, 0.19) and it is better specified, measuring tau on the stock actually left at the horizon rather than on nameplate reserves. It changes almost nothing: exports 23,101 -&gt; 23,070 PJ and every rent identical to 2dp, for 40% more solve time. The reason is that the salvage credit and the reserve dual are PERFECTLY SUBSTITUTABLE -- both are linear in cumulative production -- so lowering the credit just raises the dual one-for-one (8.64/0.00, 2.57/1.77, 0.00/4.17, all totalling 8.07 or 4.17). Turn it back on only if reserve_limit is ever replaced by a per-year stock. See TODO item 16.</t>
+          <t>How each load bin becomes a representative day. MEDOID picks a REAL day -- the one whose total demand sits closest to the bin's mean. MEAN averages the bin. Averaging destroys COINCIDENCE, not just level: a real cold day is cold in Melbourne and Adelaide and Sydney at once, which is exactly when the corridors bind, while a mean spreads the same energy over node-day combinations that never co-occurred. The network then never looks tight and the investment layer sees no congestion to build around. Adding bins does not help because each bin is still an average -- 13, 37 and 61 representative days gave byte-identical build lists. Annual energy fidelity is unaffected (measured +2.09% medoid against +2.26% mean, both dominated by the peak day's extra weight).</t>
         </is>
       </c>
     </row>
@@ -2024,18 +2026,43 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>salvage_max_passes</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>passes</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>OFF by default, as a MEASURED negative result, not an oversight. The iteration works -- it converges geometrically in 4 passes (tau moves 1.48, 0.74, 0.37, 0.19) and it is better specified, measuring tau on the stock actually left at the horizon rather than on nameplate reserves. It changes almost nothing: exports 23,101 -&gt; 23,070 PJ and every rent identical to 2dp, for 40% more solve time. The reason is that the salvage credit and the reserve dual are PERFECTLY SUBSTITUTABLE -- both are linear in cumulative production -- so lowering the credit just raises the dual one-for-one (8.64/0.00, 2.57/1.77, 0.00/4.17, all totalling 8.07 or 4.17). Turn it back on only if reserve_limit is ever replaced by a per-year stock. See TODO item 16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Capacity model</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>salvage_tau_tol</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="C64" t="n">
         <v>0.25</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Stop iterating once no row moves its reserves-to-production ratio by more than this.</t>
         </is>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -990,7 +990,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Strike the terminal salvage credit on the disposal routes a basin's gas can ACTUALLY take, weighted by each route's bottleneck capacity, instead of on the single dearest destination less the tariff to reach it. Only the basins feeding the LNG trains are affected -- a basin sitting inside the market it supplies has one disposal price and keeps the old rule. Surat has two prices that differ by the liquefaction-shipping-regasification wedge ($9.79/GJ landed-import parity against $6.37/GJ export netback in 2051) and only 349 TJ/day of corridor to the dearer one against 6,300 TJ/day of deliverability, so the old rule paid the whole basin a price 6% of its gas could reach. ON. Set FALSE to reproduce runs from before the change; it moves every Queensland scarcity rent, so every result moves.</t>
+          <t>Strike the terminal salvage credit on the disposal routes a basin's gas can ACTUALLY take, weighted by each route's bottleneck capacity, instead of on the single dearest destination less the tariff to reach it. Only the basins feeding the LNG trains are affected -- a basin sitting inside the market it supplies has one disposal price and keeps the old rule. Surat has two prices that differ by the liquefaction-shipping-regasification wedge ($9.79/GJ landed-import parity against $6.37/GJ export netback in 2051) and only 349 TJ/day of corridor to the dearer one (349 of 6,300 TJ/day, 5.5%), so the old rule paid the whole basin a price 6% of its gas could reach. ON. Set FALSE to reproduce runs from before the change; it moves every Queensland scarcity rent, so every result moves.</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1252,20 +1252,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>lng_nameplate_tj_day</t>
+          <t>lng_availability</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3680</v>
+        <v>0.897</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TJ/day</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Total east coast liquefaction nameplate (100% utilisation). Mirrors lng_daily_target in lng_parameters.csv. This is the PHYSICAL ceiling on exports under netback pricing - a train cannot liquefy more than it can liquefy, however attractive the netback.</t>
+          <t>Share of a year each LNG train can actually liquefy at its Bulletin Board MDQ. An MDQ is a DAY's maximum and GARY carries no maintenance or turnaround model, so without this the fleet runs at 100% for 365 days whenever the netback is good -- 1,604 PJ/yr, which no year on record approaches. DERIVED FROM PUBLIC DATA: AEMO 2026 GSOO Figure 19 actual LNG consumption against the same 4,395 TJ/day of GBB nameplate gives 82.6% (2019), 83.4%, 87.7%, 84.6%, 85.5%, 89.7% (2024), 88.7% (2025). This is the BEST year on record, so it is a ceiling and not an expectation; the seven-year mean is 86.0%. Puts the fleet limit at 3,942 TJ/day, which is exactly what the trains consumed in 2024.</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1277,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>lng_train_shares</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>APLNG:0.3682,GLNG:0.3023,QCLNG:0.3295</t>
-        </is>
+          <t>lng_nameplate_tj_day</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3680</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>node:share</t>
+          <t>TJ/day</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026 GSOO 'G26 Processing Transmission Storage Facilities', LNG Export sheet: APLNG 9.5, GLNG 7.8, QCLNG 8.5 Mtpa</t>
+          <t>FALLBACK ONLY since 12 Sep 2026. Each train's liquefaction nameplate is now read PER FACILITY from GasBBNameplateRatingCurrent.csv (the Gas Bulletin Board), taking the PROCESS figure where the GBB publishes both process and receive: APLNG 1,591 + GLNG 1,384 + QCLNG 1,420 = 4,395 TJ/day. This total, 3,680, is used only if that file is missing. It was too small to serve GARY's own input -- the 2026 GSOO's LNG consumption is 3,757 TJ/day in 2025 and peaks at 3,875 in 2029, and the trains actually consumed 3,942 TJ/day in 2024 -- so it silently clipped ~27 PJ/yr off every early year and pinned every scenario at exactly 1,343 PJ/yr. Checked in tests/audit_inputs.py section 12.</t>
         </is>
       </c>
     </row>
@@ -1304,72 +1302,72 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>lng_foundation_share</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0.93</v>
+          <t>lng_train_shares</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>APLNG:0.3682,GLNG:0.3023,QCLNG:0.3295</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>node:share</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Share of planned export volume committed under long-term foundation SPAs: take-or-pay, therefore price-insensitive, served whatever the netback. The remainder is the uncontracted spot tail that bids at the netback and can be outbid by a domestic buyer or taken by a reservation. DERIVED FROM PUBLIC DATA: the ACCC publishes Queensland LNG producers' uncontracted gas each quarter and reported 22 PJ available for Q1 2026 (ACCC, east coast gas supply outlook, Q1 2026); against ~325-330 PJ of quarterly exports that is ~7% uncontracted, hence 0.93. Structure confirmed by ACIL Allen (14 Nov 2025) 2.3.2: 'the supply under foundation customers is untouched in our modelling, LNG exporters then supply the domestic market and export further gas via spot cargoes'. ONE QUARTER's figure, so treat as a KEY SENSITIVITY - it sets how much export volume is contestable at all.</t>
+          <t>2026 GSOO 'G26 Processing Transmission Storage Facilities', LNG Export sheet: APLNG 9.5, GLNG 7.8, QCLNG 8.5 Mtpa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gas reservation</t>
+          <t>LNG trains</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>reservation_respects_contracts</t>
+          <t>lng_foundation_share</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1=yes, 0=no</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Default for whether a reservation may only take UNCONTRACTED export volume. 1: the reservation bites on the spot tail first and is capped at (1 - lng_foundation_share) of planned volume, so foundation SPAs are not broken - which is how the Heads of Agreement with the east coast LNG exporters actually works. 0: the reservation takes its share of ALL export volume, foundation contracts included. The dashboard toggle overrides this.</t>
+          <t>Share of planned export volume committed under long-term foundation SPAs: take-or-pay, therefore price-insensitive, served whatever the netback. The remainder is the uncontracted spot tail that bids at the netback and can be outbid by a domestic buyer or taken by a reservation. DERIVED FROM PUBLIC DATA: the ACCC publishes Queensland LNG producers' uncontracted gas each quarter and reported 22 PJ available for Q1 2026 (ACCC, east coast gas supply outlook, Q1 2026); against ~325-330 PJ of quarterly exports that is ~7% uncontracted, hence 0.93. Structure confirmed by ACIL Allen (14 Nov 2025) 2.3.2: 'the supply under foundation customers is untouched in our modelling, LNG exporters then supply the domestic market and export further gas via spot cargoes'. ONE QUARTER's figure, so treat as a KEY SENSITIVITY - it sets how much export volume is contestable at all.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Capacity model</t>
+          <t>Gas reservation</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>gsoo_expansions_only</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
+          <t>reservation_respects_contracts</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>1=yes, 0=no</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Default for the GSOO-only expansion filter. FALSE = the capacity layer may choose any candidate in expansion_options.csv; TRUE = only rows with Source=GSOO, i.e. those AEMO NAMES in its 2026 GSOO material (the G26 Field Developments sheet for supply, the GSOO/VGPR project set for pipelines) -- whatever status AEMO gives them, Committed or Undeveloped alike. Source records where a candidate came from, NOT whether it is committed. Market rows are ones GARY researched from public announcements or built itself. Overridden per run by the dashboard toggle or --gsoo-expansions-only</t>
+          <t>Default for whether a reservation may only take UNCONTRACTED export volume. 1: the reservation bites on the spot tail first and is capped at (1 - lng_foundation_share) of planned volume, so foundation SPAs are not broken - which is how the Heads of Agreement with the east coast LNG exporters actually works. 0: the reservation takes its share of ALL export volume, foundation contracts included. The dashboard toggle overrides this.</t>
         </is>
       </c>
     </row>
@@ -1381,101 +1379,101 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>expansion_source_gsoo</t>
+          <t>gsoo_expansions_only</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GSOO</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Value of the Source column in expansion_options.csv that counts as AEMO-sourced</t>
+          <t>Default for the GSOO-only expansion filter. FALSE = the capacity layer may choose any candidate in expansion_options.csv; TRUE = only rows with Source=GSOO, i.e. those AEMO NAMES in its 2026 GSOO material (the G26 Field Developments sheet for supply, the GSOO/VGPR project set for pipelines) -- whatever status AEMO gives them, Committed or Undeveloped alike. Source records where a candidate came from, NOT whether it is committed. Market rows are ones GARY researched from public announcements or built itself. Overridden per run by the dashboard toggle or --gsoo-expansions-only</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ACIL Allen LNG price</t>
+          <t>Capacity model</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>netback_pricing_default</t>
+          <t>expansion_source_gsoo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>GSOO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>label</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Default state of the dashboard's LNG netback pricing switch. TRUE = ACIL Allen price formation is on unless turned off, which is the methodology behind the 2026 GSOO and the only mode in which an international price disciplines domestic prices. Overridden per run by the sidebar switch or --netback-pricing</t>
+          <t>Value of the Source column in expansion_options.csv that counts as AEMO-sourced</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>ACIL Allen LNG price</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>storage_opening_fraction</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0.5</v>
+          <t>netback_pricing_default</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>fraction of capacity</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GARY's own. Inventory each year opens at this share of capacity and must close at or above it, so a year cannot create gas. Each year is solved independently, so this is an assumption either way.</t>
+          <t>Default state of the dashboard's LNG netback pricing switch. TRUE = ACIL Allen price formation is on unless turned off, which is the methodology behind the 2026 GSOO and the only mode in which an international price disciplines domestic prices. Overridden per run by the sidebar switch or --netback-pricing</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GSOO baselines</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>gsoo_baselines</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>StepChange,Accelerated,SlowerGrowth</t>
-        </is>
+          <t>storage_opening_fraction</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>slugs</t>
+          <t>fraction of capacity</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>The three 2026 GSOO demand scenarios GARY exposes as baselines. Was a SCENARIOS list repeated in four builder modules.</t>
+          <t>GARY's own. Inventory each year opens at this share of capacity and must close at or above it, so a year cannot create gas. Each year is solved independently, so this is an assumption either way.</t>
         </is>
       </c>
     </row>
@@ -1487,20 +1485,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>gsoo_index_base_year</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>2026</v>
+          <t>gsoo_baselines</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>StepChange,Accelerated,SlowerGrowth</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>slugs</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Year the GSOO sector indices are struck relative to.</t>
+          <t>The three 2026 GSOO demand scenarios GARY exposes as baselines. Was a SCENARIOS list repeated in four builder modules.</t>
         </is>
       </c>
     </row>
@@ -1512,11 +1512,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>gsoo_index_last_year</t>
+          <t>gsoo_index_base_year</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2045</v>
+        <v>2026</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1525,32 +1525,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Last year the 2026 GSOO publishes. Indices clamp here and hold flat to horizon_end, so 2046-2050 is EXTRAPOLATION while ACIL Allen's price series keeps moving.</t>
+          <t>Year the GSOO sector indices are struck relative to.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Seasonality</t>
+          <t>GSOO baselines</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>summer_day_start</t>
+          <t>gsoo_index_last_year</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>335</v>
+        <v>2045</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>day of year</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Southern summer window used to strike the GPG winter:summer peak ratio (wraps the year end with summer_day_end).</t>
+          <t>Last year the 2026 GSOO publishes. Indices clamp here and hold flat to horizon_end, so 2046-2050 is EXTRAPOLATION while ACIL Allen's price series keeps moving.</t>
         </is>
       </c>
     </row>
@@ -1562,11 +1562,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>summer_day_end</t>
+          <t>summer_day_start</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>59</v>
+        <v>335</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1575,57 +1575,57 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>See summer_day_start.</t>
+          <t>Southern summer window used to strike the GPG winter:summer peak ratio (wraps the year end with summer_day_end).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Demand history</t>
+          <t>Seasonality</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>gbb_recent_from</t>
+          <t>summer_day_end</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2022</v>
+        <v>59</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>day of year</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>First year of GBB actuals averaged into the representative daily shape.</t>
+          <t>See summer_day_start.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NT demand</t>
+          <t>Demand history</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nt_darwin_commercial_tjd</t>
+          <t>gbb_recent_from</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.6</v>
+        <v>2022</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TJ/day</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Darwin city-gate commercial / light-industrial load, held flat. AER AGP access arrangement review (AAR 2026-31) Table 2-1, 2024-25: Darwin distribution 0.3 + Townend Road 0.2 + Elliot 0.1.</t>
+          <t>First year of GBB actuals averaged into the representative daily shape.</t>
         </is>
       </c>
     </row>
@@ -1637,22 +1637,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nt_gpg_base_tjd</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Darwin:33.4,Amadeus:11.0</t>
-        </is>
+          <t>nt_darwin_commercial_tjd</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.6</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>node:TJ/day</t>
+          <t>TJ/day</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NT gas-fired generation by node in 2026, from AER AAR 2026-31 Table 2-1 delivery points, assigned by which side of Tennant Creek they sit on.</t>
+          <t>Darwin city-gate commercial / light-industrial load, held flat. AER AGP access arrangement review (AAR 2026-31) Table 2-1, 2024-25: Darwin distribution 0.3 + Townend Road 0.2 + Elliot 0.1.</t>
         </is>
       </c>
     </row>
@@ -1664,74 +1662,74 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nt_gpg_decline</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.008</v>
+          <t>nt_gpg_base_tjd</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Darwin:33.4,Amadeus:11.0</t>
+        </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>fraction/yr</t>
+          <t>node:TJ/day</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gentle solar-driven decline on NT GPG. GARY's own; the NT is outside the NEM and the GSOO scenario framework.</t>
+          <t>NT gas-fired generation by node in 2026, from AER AAR 2026-31 Table 2-1 delivery points, assigned by which side of Tennant Creek they sit on.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GSOO baselines</t>
+          <t>NT demand</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gpg_nem_regions</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>NSW,SA,VIC,QLD</t>
-        </is>
+          <t>nt_gpg_decline</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.008</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>regions</t>
+          <t>fraction/yr</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>NEM regions whose GPG is re-based on the GSOO. The NT is outside the NEM and the GSOO scenario framework, so it is sized separately from the AER's AGP access arrangement; TAS has no modelled node.</t>
+          <t>Gentle solar-driven decline on NT GPG. GARY's own; the NT is outside the NEM and the GSOO scenario framework.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Demand shape</t>
+          <t>GSOO baselines</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>peak_shape_matching</t>
+          <t>gpg_nem_regions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>NSW,SA,VIC,QLD</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>regions</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Reshape each city-gate node's daily profile year by year so its winter peak matches the 2026 GSOO's regional RC&amp;I daily maximum, holding annual energy fixed. Without it the 2026 daily shape is frozen for 26 years while the load behind it shifts from heating to industrial, so VIC's peak ran 22% over AEMO in 2026 and 43% over by 2045.</t>
+          <t>NEM regions whose GPG is re-based on the GSOO. The NT is outside the NEM and the GSOO scenario framework, so it is sized separately from the AER's AGP access arrangement; TAS has no modelled node.</t>
         </is>
       </c>
     </row>
@@ -1743,20 +1741,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>peak_shape_k_min</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.25</v>
+          <t>peak_shape_matching</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>multiple</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lower clip on the peakiness rescale. A region whose ANNUAL energy coverage is short cannot have its peak matched by reshaping alone (QLD: GARY carries no industrial outside Gladstone, TODO item 10), so the rescale is bounded and the residual is reported rather than forced.</t>
+          <t>Reshape each city-gate node's daily profile year by year so its winter peak matches the 2026 GSOO's regional RC&amp;I daily maximum, holding annual energy fixed. Without it the 2026 daily shape is frozen for 26 years while the load behind it shifts from heating to industrial, so VIC's peak ran 22% over AEMO in 2026 and 43% over by 2045.</t>
         </is>
       </c>
     </row>
@@ -1768,11 +1768,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>peak_shape_k_max</t>
+          <t>peak_shape_k_min</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1781,59 +1781,59 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Upper clip on the peakiness rescale. See peak_shape_k_min.</t>
+          <t>Lower clip on the peakiness rescale. A region whose ANNUAL energy coverage is short cannot have its peak matched by reshaping alone (QLD: GARY carries no industrial outside Gladstone, TODO item 10), so the rescale is bounded and the residual is reported rather than forced.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Capacity model</t>
+          <t>Demand shape</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>allow_import_terminals</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+          <t>peak_shape_k_max</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2.5</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Whether the capacity layer may build LNG IMPORT terminals -- a Type=Terminal candidate whose Target is one of import_nodes (Port Kembla, Geelong, Adelaide). FALSE removes them from the candidate set, so the east coast must meet demand from domestic supply and pipe. Field developments (Golden Beach, Beetaloo) are also Type=Terminal but target basin nodes, so they are NOT affected.</t>
+          <t>Upper clip on the peakiness rescale. See peak_shape_k_min.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cost coefficients</t>
+          <t>Capacity model</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>capex_annualisation_rate</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>0.08</v>
+          <t>allow_import_terminals</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Share of a built project's CapEx charged to each single-year dispatch solve. The dispatch model covers one year and has no NPV to charge a lump sum against, so a build has to show up as an annual carrying cost or it would look free. GARY's own number, not a source: it sits above discount_rate_default because it stands in for return OF capital as well as return ON it. The capacity MIP does NOT use it -- that layer charges full CapEx once, discounted to the build year.</t>
+          <t>Whether the capacity layer may build LNG IMPORT terminals -- a Type=Terminal candidate whose Target is one of import_nodes (Port Kembla, Geelong, Adelaide). FALSE removes them from the candidate set, so the east coast must meet demand from domestic supply and pipe. Field developments (Golden Beach, Beetaloo) are also Type=Terminal but target basin nodes, so they are NOT affected.</t>
         </is>
       </c>
     </row>
@@ -1845,72 +1845,70 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>storage_cycle_cost</t>
+          <t>capex_annualisation_rate</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A$/GJ</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Round-trip charge on storage, applied to injection AND withdrawal, so inventory cycles only when the seasonal price spread justifies it. GARY's own number, not a source. Read by both the dispatch model and the capacity MIP so the two layers value a store identically.</t>
+          <t>Share of a built project's CapEx charged to each single-year dispatch solve. The dispatch model covers one year and has no NPV to charge a lump sum against, so a build has to show up as an annual carrying cost or it would look free. GARY's own number, not a source: it sits above discount_rate_default because it stands in for return OF capital as well as return ON it. The capacity MIP does NOT use it -- that layer charges full CapEx once, discounted to the build year.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Horizon</t>
+          <t>Cost coefficients</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>horizon_report_end</t>
+          <t>storage_cycle_cost</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2050</v>
+        <v>0.5</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>A$/GJ</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Last year PRESENTED. Results beyond this are solved but trimmed off before they reach the dashboard or a caller -- see solve.solve_scenario. Keep it strictly below horizon_end.</t>
+          <t>Round-trip charge on storage, applied to injection AND withdrawal, so inventory cycles only when the seasonal price spread justifies it. GARY's own number, not a source. Read by both the dispatch model and the capacity MIP so the two layers value a store identically.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Dashboard defaults</t>
+          <t>Horizon</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>winter_default</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>horizon_report_end</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2050</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Winter level the dashboard opens on. MEDIUM is the central GSOO case (multiplier 1.0, AEMO's weather-averaged series). Low is an unseasonably warm winter (0.91x) and High a deliberate stress (1.5x) beyond any observed winter.</t>
+          <t>Last year PRESENTED. Results beyond this are solved but trimmed off before they reach the dashboard or a caller -- see solve.solve_scenario. Keep it strictly below horizon_end.</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1920,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>lng_default</t>
+          <t>winter_default</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1937,7 +1935,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Global LNG price level the dashboard opens on. Under netback pricing this lever selects a PRICE path, not an export volume: Medium is the run's own GSOO scenario path, so it is the internally consistent choice. Low is ACIL Allen's Accelerated Transition path and High its Slower Growth path.</t>
+          <t>Winter level the dashboard opens on. MEDIUM is the central GSOO case (multiplier 1.0, AEMO's weather-averaged series). Low is an unseasonably warm winter (0.91x) and High a deliberate stress (1.5x) beyond any observed winter.</t>
         </is>
       </c>
     </row>
@@ -1949,45 +1947,47 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>mip_gap_default</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>0.005</v>
+          <t>lng_default</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Relative MIP gap for the capacity layer. Matches solve_scenario's own default; the dashboard slider used to open at 0.01, which is a wider tolerance than any headless run used. That matters more since field developments carry derived CapEx in the tens of billions -- 1% of the objective is enough to hide a build decision.</t>
+          <t>Global LNG price level the dashboard opens on. Under netback pricing this lever selects a PRICE path, not an export volume: Medium is the run's own GSOO scenario path, so it is the internally consistent choice. Low is ACIL Allen's Accelerated Transition path and High its Slower Growth path.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Capacity model</t>
+          <t>Dashboard defaults</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>rep_bins_per_month</t>
+          <t>mip_gap_default</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>0.005</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Load bins per month in the capacity layer's representative days. 1 reproduces the old single monthly MEAN day, which flattens the load-duration curve inside the month: a mild day and a cold snap in the same July became one average July day, and the marginal supply differs between them. Measured 30 Aug 2026 at 1 bin, the MIP planned ~44 PJ/yr LESS southern production than the 365-day dispatch layer drew, three years running, exhausting the southern tranches a year early and putting 16,008 TJ of shortage into 2032 the MIP never saw. Cost is roughly linear in the bin count: 3 bins is 37 representative days a year against 13.</t>
+          <t>Relative MIP gap for the capacity layer. Matches solve_scenario's own default; the dashboard slider used to open at 0.01, which is a wider tolerance than any headless run used. That matters more since field developments carry derived CapEx in the tens of billions -- 1% of the objective is enough to hide a build decision.</t>
         </is>
       </c>
     </row>
@@ -1999,22 +1999,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>rep_day_mode</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>medoid</t>
-        </is>
+          <t>rep_bins_per_month</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>3</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>mean|medoid</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>How each load bin becomes a representative day. MEDOID picks a REAL day -- the one whose total demand sits closest to the bin's mean. MEAN averages the bin. Averaging destroys COINCIDENCE, not just level: a real cold day is cold in Melbourne and Adelaide and Sydney at once, which is exactly when the corridors bind, while a mean spreads the same energy over node-day combinations that never co-occurred. The network then never looks tight and the investment layer sees no congestion to build around. Adding bins does not help because each bin is still an average -- 13, 37 and 61 representative days gave byte-identical build lists. Annual energy fidelity is unaffected (measured +2.09% medoid against +2.26% mean, both dominated by the peak day's extra weight).</t>
+          <t>Load bins per month in the capacity layer's representative days. 1 reproduces the old single monthly MEAN day, which flattens the load-duration curve inside the month: a mild day and a cold snap in the same July became one average July day, and the marginal supply differs between them. Measured 30 Aug 2026 at 1 bin, the MIP planned ~44 PJ/yr LESS southern production than the 365-day dispatch layer drew, three years running, exhausting the southern tranches a year early and putting 16,008 TJ of shortage into 2032 the MIP never saw. Cost is roughly linear in the bin count: 3 bins is 37 representative days a year against 13.</t>
         </is>
       </c>
     </row>
@@ -2026,20 +2024,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>salvage_max_passes</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>0</v>
+          <t>rep_day_mode</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>medoid</t>
+        </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>passes</t>
+          <t>mean|medoid</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OFF by default, as a MEASURED negative result, not an oversight. The iteration works -- it converges geometrically in 4 passes (tau moves 1.48, 0.74, 0.37, 0.19) and it is better specified, measuring tau on the stock actually left at the horizon rather than on nameplate reserves. It changes almost nothing: exports 23,101 -&gt; 23,070 PJ and every rent identical to 2dp, for 40% more solve time. The reason is that the salvage credit and the reserve dual are PERFECTLY SUBSTITUTABLE -- both are linear in cumulative production -- so lowering the credit just raises the dual one-for-one (8.64/0.00, 2.57/1.77, 0.00/4.17, all totalling 8.07 or 4.17). Turn it back on only if reserve_limit is ever replaced by a per-year stock. See TODO item 16.</t>
+          <t>How each load bin becomes a representative day. MEDOID picks a REAL day -- the one whose total demand sits closest to the bin's mean. MEAN averages the bin. Averaging destroys COINCIDENCE, not just level: a real cold day is cold in Melbourne and Adelaide and Sydney at once, which is exactly when the corridors bind, while a mean spreads the same energy over node-day combinations that never co-occurred. The network then never looks tight and the investment layer sees no congestion to build around. Adding bins does not help because each bin is still an average -- 13, 37 and 61 representative days gave byte-identical build lists. Annual energy fidelity is unaffected (measured +2.09% medoid against +2.26% mean, both dominated by the peak day's extra weight).</t>
         </is>
       </c>
     </row>
@@ -2051,18 +2051,43 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>salvage_max_passes</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>passes</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>OFF by default, as a MEASURED negative result, not an oversight. The iteration works -- it converges geometrically in 4 passes (tau moves 1.48, 0.74, 0.37, 0.19) and it is better specified, measuring tau on the stock actually left at the horizon rather than on nameplate reserves. It changes almost nothing: exports 23,101 -&gt; 23,070 PJ and every rent identical to 2dp, for 40% more solve time. The reason is that the salvage credit and the reserve dual are PERFECTLY SUBSTITUTABLE -- both are linear in cumulative production -- so lowering the credit just raises the dual one-for-one (8.64/0.00, 2.57/1.77, 0.00/4.17, all totalling 8.07 or 4.17). Turn it back on only if reserve_limit is ever replaced by a per-year stock. See TODO item 16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Capacity model</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>salvage_tau_tol</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="C65" t="n">
         <v>0.25</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Stop iterating once no row moves its reserves-to-production ratio by more than this.</t>
         </is>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1845,70 +1845,72 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>capex_annualisation_rate</t>
+          <t>storage_cycle_cost</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>A$/GJ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Share of a built project's CapEx charged to each single-year dispatch solve. The dispatch model covers one year and has no NPV to charge a lump sum against, so a build has to show up as an annual carrying cost or it would look free. GARY's own number, not a source: it sits above discount_rate_default because it stands in for return OF capital as well as return ON it. The capacity MIP does NOT use it -- that layer charges full CapEx once, discounted to the build year.</t>
+          <t>Round-trip charge on storage, applied to injection AND withdrawal, so inventory cycles only when the seasonal price spread justifies it. GARY's own number, not a source. Read by both the dispatch model and the capacity MIP so the two layers value a store identically.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cost coefficients</t>
+          <t>Horizon</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>storage_cycle_cost</t>
+          <t>horizon_report_end</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.5</v>
+        <v>2050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A$/GJ</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Round-trip charge on storage, applied to injection AND withdrawal, so inventory cycles only when the seasonal price spread justifies it. GARY's own number, not a source. Read by both the dispatch model and the capacity MIP so the two layers value a store identically.</t>
+          <t>Last year PRESENTED. Results beyond this are solved but trimmed off before they reach the dashboard or a caller -- see solve.solve_scenario. Keep it strictly below horizon_end.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Horizon</t>
+          <t>Dashboard defaults</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>horizon_report_end</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>2050</v>
+          <t>winter_default</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Last year PRESENTED. Results beyond this are solved but trimmed off before they reach the dashboard or a caller -- see solve.solve_scenario. Keep it strictly below horizon_end.</t>
+          <t>Winter level the dashboard opens on. MEDIUM is the central GSOO case (multiplier 1.0, AEMO's weather-averaged series). Low is an unseasonably warm winter (0.91x) and High a deliberate stress (1.5x) beyond any observed winter.</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1922,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>winter_default</t>
+          <t>lng_default</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1935,7 +1937,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Winter level the dashboard opens on. MEDIUM is the central GSOO case (multiplier 1.0, AEMO's weather-averaged series). Low is an unseasonably warm winter (0.91x) and High a deliberate stress (1.5x) beyond any observed winter.</t>
+          <t>Global LNG price level the dashboard opens on. Under netback pricing this lever selects a PRICE path, not an export volume: Medium is the run's own GSOO scenario path, so it is the internally consistent choice. Low is ACIL Allen's Accelerated Transition path and High its Slower Growth path.</t>
         </is>
       </c>
     </row>
@@ -1947,47 +1949,45 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>lng_default</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
+          <t>mip_gap_default</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.0001</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Global LNG price level the dashboard opens on. Under netback pricing this lever selects a PRICE path, not an export volume: Medium is the run's own GSOO scenario path, so it is the internally consistent choice. Low is ACIL Allen's Accelerated Transition path and High its Slower Growth path.</t>
+          <t>Relative MIP gap for the capacity layer. Measured 23 Sep 2026 on the central case: at 0.005 the solver stopped $104m from its bound and built one project fewer (NGP_Reversal) and Bulloo a year later than at 0.0001, which closed to $7m in 111 s against 15 s. The relative gap is on the WHOLE-SYSTEM NPV (~$94bn), so 0.5% allowed ~$470m -- more than most candidates cost. HiGHS stops at whichever of this and mip_abs_gap_aud is met first.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dashboard defaults</t>
+          <t>Capacity model</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>mip_gap_default</t>
+          <t>rep_bins_per_month</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.005</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>count</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Relative MIP gap for the capacity layer. Matches solve_scenario's own default; the dashboard slider used to open at 0.01, which is a wider tolerance than any headless run used. That matters more since field developments carry derived CapEx in the tens of billions -- 1% of the objective is enough to hide a build decision.</t>
+          <t>Load bins per month in the capacity layer's representative days. 1 reproduces the old single monthly MEAN day, which flattens the load-duration curve inside the month: a mild day and a cold snap in the same July became one average July day, and the marginal supply differs between them. Measured 30 Aug 2026 at 1 bin, the MIP planned ~44 PJ/yr LESS southern production than the 365-day dispatch layer drew, three years running, exhausting the southern tranches a year early and putting 16,008 TJ of shortage into 2032 the MIP never saw. Cost is roughly linear in the bin count: 3 bins is 37 representative days a year against 13.</t>
         </is>
       </c>
     </row>
@@ -1999,20 +1999,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>rep_bins_per_month</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>3</v>
+          <t>rep_day_mode</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>medoid</t>
+        </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>mean|medoid</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Load bins per month in the capacity layer's representative days. 1 reproduces the old single monthly MEAN day, which flattens the load-duration curve inside the month: a mild day and a cold snap in the same July became one average July day, and the marginal supply differs between them. Measured 30 Aug 2026 at 1 bin, the MIP planned ~44 PJ/yr LESS southern production than the 365-day dispatch layer drew, three years running, exhausting the southern tranches a year early and putting 16,008 TJ of shortage into 2032 the MIP never saw. Cost is roughly linear in the bin count: 3 bins is 37 representative days a year against 13.</t>
+          <t>How each load bin becomes a representative day. MEDOID picks a REAL day -- the one whose total demand sits closest to the bin's mean. MEAN averages the bin. Averaging destroys COINCIDENCE, not just level: a real cold day is cold in Melbourne and Adelaide and Sydney at once, which is exactly when the corridors bind, while a mean spreads the same energy over node-day combinations that never co-occurred. The network then never looks tight and the investment layer sees no congestion to build around. Adding bins does not help because each bin is still an average -- 13, 37 and 61 representative days gave byte-identical build lists. Annual energy fidelity is unaffected (measured +2.09% medoid against +2.26% mean, both dominated by the peak day's extra weight).</t>
         </is>
       </c>
     </row>
@@ -2024,22 +2026,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>rep_day_mode</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>medoid</t>
-        </is>
+          <t>salvage_max_passes</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>mean|medoid</t>
+          <t>passes</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>How each load bin becomes a representative day. MEDOID picks a REAL day -- the one whose total demand sits closest to the bin's mean. MEAN averages the bin. Averaging destroys COINCIDENCE, not just level: a real cold day is cold in Melbourne and Adelaide and Sydney at once, which is exactly when the corridors bind, while a mean spreads the same energy over node-day combinations that never co-occurred. The network then never looks tight and the investment layer sees no congestion to build around. Adding bins does not help because each bin is still an average -- 13, 37 and 61 representative days gave byte-identical build lists. Annual energy fidelity is unaffected (measured +2.09% medoid against +2.26% mean, both dominated by the peak day's extra weight).</t>
+          <t>OFF by default, as a MEASURED negative result, not an oversight. The iteration works -- it converges geometrically in 4 passes (tau moves 1.48, 0.74, 0.37, 0.19) and it is better specified, measuring tau on the stock actually left at the horizon rather than on nameplate reserves. It changes almost nothing: exports 23,101 -&gt; 23,070 PJ and every rent identical to 2dp, for 40% more solve time. The reason is that the salvage credit and the reserve dual are PERFECTLY SUBSTITUTABLE -- both are linear in cumulative production -- so lowering the credit just raises the dual one-for-one (8.64/0.00, 2.57/1.77, 0.00/4.17, all totalling 8.07 or 4.17). Turn it back on only if reserve_limit is ever replaced by a per-year stock. See TODO item 16.</t>
         </is>
       </c>
     </row>
@@ -2051,20 +2051,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>salvage_max_passes</t>
+          <t>salvage_tau_tol</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>passes</t>
+          <t>years</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OFF by default, as a MEASURED negative result, not an oversight. The iteration works -- it converges geometrically in 4 passes (tau moves 1.48, 0.74, 0.37, 0.19) and it is better specified, measuring tau on the stock actually left at the horizon rather than on nameplate reserves. It changes almost nothing: exports 23,101 -&gt; 23,070 PJ and every rent identical to 2dp, for 40% more solve time. The reason is that the salvage credit and the reserve dual are PERFECTLY SUBSTITUTABLE -- both are linear in cumulative production -- so lowering the credit just raises the dual one-for-one (8.64/0.00, 2.57/1.77, 0.00/4.17, all totalling 8.07 or 4.17). Turn it back on only if reserve_limit is ever replaced by a per-year stock. See TODO item 16.</t>
+          <t>Stop iterating once no row moves its reserves-to-production ratio by more than this.</t>
         </is>
       </c>
     </row>
@@ -2076,20 +2076,147 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>salvage_tau_tol</t>
+          <t>mip_abs_gap_aud</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.25</v>
+        <v>10000000</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>A$</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stop iterating once no row moves its reserves-to-production ratio by more than this.</t>
+          <t>Absolute MIP gap, dollars of objective. Set well below the smallest candidate CapEx ($24m) so the solver cannot stop with a build decision unsettled. HiGHS only; GLPK has no absolute gap and uses mip_gap_default alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Solver</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>solver_threads_default</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>4</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>threads</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>HiGHS threads per solve when GARY_SOLVER_THREADS is not set. Parallel sweeps pin their workers to 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Seasonality</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>winter_nodes</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Melbourne,Adelaide,Sydney</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>nodes</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Nodes whose distribution demand the Winter lever multiplies over winter_day_start..winter_day_end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Scenario levers</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>lng_low_decline_after</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>fraction/yr</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LNG Low (netback pricing OFF only): annual fall in the export volume multiplier after the Scenario_Levers LNG/Low window, continuing from wherever the window ended. See solve.get_lng_mult.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Scenario levers</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>lng_low_floor</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>LNG Low (netback pricing OFF only): floor on the export volume multiplier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Scenario levers</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>lng_high_outside_window</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LNG High (netback pricing OFF only): export volume multiplier outside the Scenario_Levers LNG/High window.</t>
         </is>
       </c>
     </row>

--- a/src/data/gary_parameters.xlsx
+++ b/src/data/gary_parameters.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gas Market Code cap, ACIL Allen (14 Nov 2025) 2.3.1; applied as a ceiling on the LNG netback per ACIL Allen (14 Jul 2023) 4.1. Self-terminating: once the netback falls below it the ceiling stops binding.</t>
+          <t>Gas Market Code cap, ACIL Allen (14 Nov 2025) 2.3.1; applied as a ceiling on the LNG netback per ACIL Allen (14 Jul 2023) 2.6.1. Self-terminating: once the netback falls below it the ceiling stops binding.</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Weak global LNG demand: ACIL Allen's Accelerated Transition price path (netback $7.33/GJ in 2030, $3.94 by 2050)</t>
+          <t>Weak global LNG demand: ACIL Allen's Accelerated Transition LNG price path (14 Nov 2025, Table B.4). GARY's netback off it (less export_netback_deduction): $7.33/GJ in 2030, $3.94 by 2050</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strong global LNG demand: ACIL Allen's Slower Growth price path (netback $10.39/GJ in 2030, at the $12 Code cap from 2040)</t>
+          <t>Strong global LNG demand: ACIL Allen's Slower Growth LNG price path (14 Nov 2025, Table B.4). GARY's netback off it: $10.39/GJ in 2030, at the $12 Code cap from 2040</t>
         </is>
       </c>
     </row>
